--- a/BaoCao_Final/11.SprintBacklog.xlsx
+++ b/BaoCao_Final/11.SprintBacklog.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cuong\Downloads\BaoCao_Final (2)\BaoCao_Final\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BaoCao_Final (5) - File Sửa\BaoCao_Final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD4D0D8-972B-4BB3-8A92-BE0DDB3EDD6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F97BFC-D57C-4520-86FD-0486CDFFDAB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1050,14 +1050,50 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1067,42 +1103,6 @@
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2479,13 +2479,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>144</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:rowOff>176039</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>388962</xdr:colOff>
-      <xdr:row>160</xdr:row>
-      <xdr:rowOff>206188</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>404091</xdr:colOff>
+      <xdr:row>164</xdr:row>
+      <xdr:rowOff>23090</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2523,10 +2523,10 @@
       <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>155880</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>92380</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>23090</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>11546</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2748,7 +2748,7 @@
     <col min="33" max="16384" width="8.81640625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" ht="17" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2947,12 +2947,12 @@
     </row>
     <row r="6" spans="1:32" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
@@ -3257,10 +3257,10 @@
     </row>
     <row r="13" spans="1:32" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
-      <c r="B13" s="54" t="s">
+      <c r="B13" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="54"/>
+      <c r="C13" s="51"/>
       <c r="D13" s="19">
         <f>SUM(D8:D12)</f>
         <v>310.5</v>
@@ -3338,14 +3338,14 @@
       <c r="B15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="55" t="s">
+      <c r="C15" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55" t="s">
+      <c r="D15" s="52"/>
+      <c r="E15" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="55"/>
+      <c r="F15" s="52"/>
       <c r="G15" s="1" t="s">
         <v>14</v>
       </c>
@@ -3418,18 +3418,18 @@
       </c>
     </row>
     <row r="16" spans="1:32" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="42" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="41" t="s">
+      <c r="A16" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="42" t="s">
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="42"/>
+      <c r="F16" s="45"/>
       <c r="G16" s="8">
         <f>4</f>
         <v>4</v>
@@ -3487,16 +3487,16 @@
       </c>
     </row>
     <row r="17" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="42"/>
-      <c r="B17" s="41" t="s">
+      <c r="A17" s="45"/>
+      <c r="B17" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="42" t="s">
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="42"/>
+      <c r="F17" s="45"/>
       <c r="G17" s="8">
         <f t="shared" ref="G17:G58" si="1">H17</f>
         <v>4</v>
@@ -3554,16 +3554,16 @@
       </c>
     </row>
     <row r="18" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="42"/>
-      <c r="B18" s="41" t="s">
+      <c r="A18" s="45"/>
+      <c r="B18" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="42" t="s">
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="42"/>
+      <c r="F18" s="45"/>
       <c r="G18" s="8">
         <f>H18</f>
         <v>2</v>
@@ -3621,18 +3621,18 @@
       </c>
     </row>
     <row r="19" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="42"/>
-      <c r="B19" s="40" t="s">
+      <c r="A19" s="45"/>
+      <c r="B19" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="41" t="s">
+      <c r="C19" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="41"/>
-      <c r="E19" s="42" t="s">
+      <c r="D19" s="46"/>
+      <c r="E19" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="42"/>
+      <c r="F19" s="45"/>
       <c r="G19" s="8">
         <f>H19</f>
         <v>0.5</v>
@@ -3690,16 +3690,16 @@
       </c>
     </row>
     <row r="20" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="42"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="41" t="s">
+      <c r="A20" s="45"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="41"/>
-      <c r="E20" s="42" t="s">
+      <c r="D20" s="46"/>
+      <c r="E20" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="42"/>
+      <c r="F20" s="45"/>
       <c r="G20" s="8">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -3757,16 +3757,16 @@
       </c>
     </row>
     <row r="21" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="42"/>
-      <c r="B21" s="42"/>
-      <c r="C21" s="41" t="s">
+      <c r="A21" s="45"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="41"/>
-      <c r="E21" s="42" t="s">
+      <c r="D21" s="46"/>
+      <c r="E21" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="F21" s="42"/>
+      <c r="F21" s="45"/>
       <c r="G21" s="8">
         <v>1.5</v>
       </c>
@@ -3823,12 +3823,12 @@
       </c>
     </row>
     <row r="22" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="42"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="52"/>
-      <c r="F22" s="53"/>
+      <c r="A22" s="45"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="48"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
@@ -3851,16 +3851,16 @@
       <c r="X22" s="8"/>
     </row>
     <row r="23" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="42"/>
-      <c r="B23" s="42"/>
-      <c r="C23" s="41" t="s">
+      <c r="A23" s="45"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="41"/>
-      <c r="E23" s="42" t="s">
+      <c r="D23" s="46"/>
+      <c r="E23" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="F23" s="42"/>
+      <c r="F23" s="45"/>
       <c r="G23" s="8">
         <v>1.5</v>
       </c>
@@ -3917,12 +3917,12 @@
       </c>
     </row>
     <row r="24" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="42"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="53"/>
+      <c r="A24" s="45"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="48"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
@@ -3945,16 +3945,16 @@
       <c r="X24" s="8"/>
     </row>
     <row r="25" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="42"/>
-      <c r="B25" s="42"/>
-      <c r="C25" s="41" t="s">
+      <c r="A25" s="45"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="41"/>
-      <c r="E25" s="42" t="s">
+      <c r="D25" s="46"/>
+      <c r="E25" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="F25" s="42"/>
+      <c r="F25" s="45"/>
       <c r="G25" s="8">
         <v>1.5</v>
       </c>
@@ -4011,12 +4011,12 @@
       </c>
     </row>
     <row r="26" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="42"/>
-      <c r="B26" s="42"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="52"/>
-      <c r="F26" s="53"/>
+      <c r="A26" s="45"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="48"/>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
@@ -4039,16 +4039,16 @@
       <c r="X26" s="8"/>
     </row>
     <row r="27" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="42"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="41" t="s">
+      <c r="A27" s="45"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="41"/>
-      <c r="E27" s="42" t="s">
+      <c r="D27" s="46"/>
+      <c r="E27" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="F27" s="42"/>
+      <c r="F27" s="45"/>
       <c r="G27" s="8">
         <v>1.5</v>
       </c>
@@ -4105,12 +4105,12 @@
       </c>
     </row>
     <row r="28" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="42"/>
-      <c r="B28" s="42"/>
-      <c r="C28" s="52"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="52"/>
-      <c r="F28" s="53"/>
+      <c r="A28" s="45"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="48"/>
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
@@ -4133,16 +4133,16 @@
       <c r="X28" s="8"/>
     </row>
     <row r="29" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="42"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="41" t="s">
+      <c r="A29" s="45"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="D29" s="41"/>
-      <c r="E29" s="42" t="s">
+      <c r="D29" s="46"/>
+      <c r="E29" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="F29" s="42"/>
+      <c r="F29" s="45"/>
       <c r="G29" s="8">
         <v>1.5</v>
       </c>
@@ -4199,12 +4199,12 @@
       </c>
     </row>
     <row r="30" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="42"/>
-      <c r="B30" s="42"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="53"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="53"/>
+      <c r="A30" s="45"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="47"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="48"/>
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
@@ -4227,16 +4227,16 @@
       <c r="X30" s="8"/>
     </row>
     <row r="31" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="42"/>
-      <c r="B31" s="42"/>
-      <c r="C31" s="41" t="s">
+      <c r="A31" s="45"/>
+      <c r="B31" s="45"/>
+      <c r="C31" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="41"/>
-      <c r="E31" s="42" t="s">
+      <c r="D31" s="46"/>
+      <c r="E31" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="F31" s="42"/>
+      <c r="F31" s="45"/>
       <c r="G31" s="8">
         <v>1.5</v>
       </c>
@@ -4293,12 +4293,12 @@
       </c>
     </row>
     <row r="32" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="42"/>
-      <c r="B32" s="42"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="53"/>
+      <c r="A32" s="45"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="48"/>
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
@@ -4321,16 +4321,16 @@
       <c r="X32" s="8"/>
     </row>
     <row r="33" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="42"/>
-      <c r="B33" s="42"/>
-      <c r="C33" s="41" t="s">
+      <c r="A33" s="45"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="D33" s="41"/>
-      <c r="E33" s="42" t="s">
+      <c r="D33" s="46"/>
+      <c r="E33" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="F33" s="42"/>
+      <c r="F33" s="45"/>
       <c r="G33" s="8">
         <v>1.5</v>
       </c>
@@ -4387,12 +4387,12 @@
       </c>
     </row>
     <row r="34" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="42"/>
-      <c r="B34" s="42"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="53"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="53"/>
+      <c r="A34" s="45"/>
+      <c r="B34" s="45"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="48"/>
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
@@ -4414,16 +4414,16 @@
       <c r="X34" s="8"/>
     </row>
     <row r="35" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="42"/>
-      <c r="B35" s="42"/>
-      <c r="C35" s="41" t="s">
+      <c r="A35" s="45"/>
+      <c r="B35" s="45"/>
+      <c r="C35" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="41"/>
-      <c r="E35" s="42" t="s">
+      <c r="D35" s="46"/>
+      <c r="E35" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F35" s="42"/>
+      <c r="F35" s="45"/>
       <c r="G35" s="8">
         <v>0.5</v>
       </c>
@@ -4480,16 +4480,16 @@
       </c>
     </row>
     <row r="36" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="42"/>
-      <c r="B36" s="42"/>
-      <c r="C36" s="41" t="s">
+      <c r="A36" s="45"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="D36" s="41"/>
-      <c r="E36" s="42" t="s">
+      <c r="D36" s="46"/>
+      <c r="E36" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F36" s="42"/>
+      <c r="F36" s="45"/>
       <c r="G36" s="8">
         <v>0.5</v>
       </c>
@@ -4546,16 +4546,16 @@
       </c>
     </row>
     <row r="37" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="42"/>
-      <c r="B37" s="42"/>
-      <c r="C37" s="41" t="s">
+      <c r="A37" s="45"/>
+      <c r="B37" s="45"/>
+      <c r="C37" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="D37" s="41"/>
-      <c r="E37" s="42" t="s">
+      <c r="D37" s="46"/>
+      <c r="E37" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F37" s="42"/>
+      <c r="F37" s="45"/>
       <c r="G37" s="8">
         <v>0.5</v>
       </c>
@@ -4612,16 +4612,16 @@
       </c>
     </row>
     <row r="38" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="42"/>
-      <c r="B38" s="40"/>
-      <c r="C38" s="41" t="s">
+      <c r="A38" s="45"/>
+      <c r="B38" s="53"/>
+      <c r="C38" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="D38" s="41"/>
-      <c r="E38" s="42" t="s">
+      <c r="D38" s="46"/>
+      <c r="E38" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F38" s="42"/>
+      <c r="F38" s="45"/>
       <c r="G38" s="8">
         <f>H38</f>
         <v>14</v>
@@ -4679,18 +4679,18 @@
       </c>
     </row>
     <row r="39" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="42"/>
-      <c r="B39" s="40" t="s">
+      <c r="A39" s="45"/>
+      <c r="B39" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="C39" s="41" t="s">
+      <c r="C39" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="D39" s="41"/>
-      <c r="E39" s="42" t="s">
+      <c r="D39" s="46"/>
+      <c r="E39" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F39" s="42"/>
+      <c r="F39" s="45"/>
       <c r="G39" s="8">
         <f>H39</f>
         <v>2</v>
@@ -4748,16 +4748,16 @@
       </c>
     </row>
     <row r="40" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="42"/>
-      <c r="B40" s="40"/>
-      <c r="C40" s="41" t="s">
+      <c r="A40" s="45"/>
+      <c r="B40" s="53"/>
+      <c r="C40" s="46" t="s">
         <v>162</v>
       </c>
-      <c r="D40" s="41"/>
-      <c r="E40" s="52" t="s">
+      <c r="D40" s="46"/>
+      <c r="E40" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="F40" s="53"/>
+      <c r="F40" s="48"/>
       <c r="G40" s="8">
         <v>1</v>
       </c>
@@ -4814,16 +4814,16 @@
       </c>
     </row>
     <row r="41" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="42"/>
-      <c r="B41" s="42"/>
-      <c r="C41" s="41" t="s">
+      <c r="A41" s="45"/>
+      <c r="B41" s="45"/>
+      <c r="C41" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="D41" s="41"/>
-      <c r="E41" s="42" t="s">
+      <c r="D41" s="46"/>
+      <c r="E41" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F41" s="42"/>
+      <c r="F41" s="45"/>
       <c r="G41" s="8">
         <f>H41</f>
         <v>2</v>
@@ -4881,16 +4881,16 @@
       </c>
     </row>
     <row r="42" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="42"/>
-      <c r="B42" s="42"/>
-      <c r="C42" s="41" t="s">
+      <c r="A42" s="45"/>
+      <c r="B42" s="45"/>
+      <c r="C42" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="D42" s="41"/>
-      <c r="E42" s="42" t="s">
+      <c r="D42" s="46"/>
+      <c r="E42" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F42" s="42"/>
+      <c r="F42" s="45"/>
       <c r="G42" s="8">
         <f>H42</f>
         <v>2</v>
@@ -4948,16 +4948,16 @@
       </c>
     </row>
     <row r="43" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="42"/>
-      <c r="B43" s="42"/>
-      <c r="C43" s="41" t="s">
+      <c r="A43" s="45"/>
+      <c r="B43" s="45"/>
+      <c r="C43" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="D43" s="41"/>
-      <c r="E43" s="42" t="s">
+      <c r="D43" s="46"/>
+      <c r="E43" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F43" s="42"/>
+      <c r="F43" s="45"/>
       <c r="G43" s="8">
         <f>H43</f>
         <v>3</v>
@@ -5015,16 +5015,16 @@
       </c>
     </row>
     <row r="44" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="42"/>
-      <c r="B44" s="42"/>
-      <c r="C44" s="41" t="s">
+      <c r="A44" s="45"/>
+      <c r="B44" s="45"/>
+      <c r="C44" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="D44" s="41"/>
-      <c r="E44" s="42" t="s">
+      <c r="D44" s="46"/>
+      <c r="E44" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F44" s="42"/>
+      <c r="F44" s="45"/>
       <c r="G44" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
@@ -5082,16 +5082,16 @@
       </c>
     </row>
     <row r="45" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="42"/>
-      <c r="B45" s="42"/>
-      <c r="C45" s="41" t="s">
+      <c r="A45" s="45"/>
+      <c r="B45" s="45"/>
+      <c r="C45" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="D45" s="41"/>
-      <c r="E45" s="42" t="s">
+      <c r="D45" s="46"/>
+      <c r="E45" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F45" s="42"/>
+      <c r="F45" s="45"/>
       <c r="G45" s="8">
         <f t="shared" ref="G45:G53" si="2">H45</f>
         <v>2</v>
@@ -5149,16 +5149,16 @@
       </c>
     </row>
     <row r="46" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="42"/>
-      <c r="B46" s="42"/>
-      <c r="C46" s="41" t="s">
+      <c r="A46" s="45"/>
+      <c r="B46" s="45"/>
+      <c r="C46" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="D46" s="41"/>
-      <c r="E46" s="42" t="s">
+      <c r="D46" s="46"/>
+      <c r="E46" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F46" s="42"/>
+      <c r="F46" s="45"/>
       <c r="G46" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
@@ -5216,16 +5216,16 @@
       </c>
     </row>
     <row r="47" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="42"/>
-      <c r="B47" s="42"/>
-      <c r="C47" s="41" t="s">
+      <c r="A47" s="45"/>
+      <c r="B47" s="45"/>
+      <c r="C47" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="D47" s="41"/>
-      <c r="E47" s="42" t="s">
+      <c r="D47" s="46"/>
+      <c r="E47" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F47" s="42"/>
+      <c r="F47" s="45"/>
       <c r="G47" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
@@ -5283,16 +5283,16 @@
       </c>
     </row>
     <row r="48" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="42"/>
-      <c r="B48" s="42"/>
-      <c r="C48" s="41" t="s">
+      <c r="A48" s="45"/>
+      <c r="B48" s="45"/>
+      <c r="C48" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="D48" s="41"/>
-      <c r="E48" s="42" t="s">
+      <c r="D48" s="46"/>
+      <c r="E48" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F48" s="42"/>
+      <c r="F48" s="45"/>
       <c r="G48" s="8">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -5350,16 +5350,16 @@
       </c>
     </row>
     <row r="49" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="42"/>
-      <c r="B49" s="42"/>
-      <c r="C49" s="41" t="s">
+      <c r="A49" s="45"/>
+      <c r="B49" s="45"/>
+      <c r="C49" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="D49" s="41"/>
-      <c r="E49" s="42" t="s">
+      <c r="D49" s="46"/>
+      <c r="E49" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F49" s="42"/>
+      <c r="F49" s="45"/>
       <c r="G49" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
@@ -5417,16 +5417,16 @@
       </c>
     </row>
     <row r="50" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="42"/>
-      <c r="B50" s="42"/>
-      <c r="C50" s="41" t="s">
+      <c r="A50" s="45"/>
+      <c r="B50" s="45"/>
+      <c r="C50" s="46" t="s">
         <v>163</v>
       </c>
-      <c r="D50" s="41"/>
-      <c r="E50" s="42" t="s">
+      <c r="D50" s="46"/>
+      <c r="E50" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F50" s="42"/>
+      <c r="F50" s="45"/>
       <c r="G50" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
@@ -5484,16 +5484,16 @@
       </c>
     </row>
     <row r="51" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="42"/>
-      <c r="B51" s="42"/>
-      <c r="C51" s="56" t="s">
+      <c r="A51" s="45"/>
+      <c r="B51" s="45"/>
+      <c r="C51" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="D51" s="57"/>
-      <c r="E51" s="52" t="s">
+      <c r="D51" s="50"/>
+      <c r="E51" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="F51" s="53"/>
+      <c r="F51" s="48"/>
       <c r="G51" s="8">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -5551,16 +5551,16 @@
       </c>
     </row>
     <row r="52" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="42"/>
-      <c r="B52" s="42"/>
-      <c r="C52" s="41" t="s">
+      <c r="A52" s="45"/>
+      <c r="B52" s="45"/>
+      <c r="C52" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="41"/>
-      <c r="E52" s="42" t="s">
+      <c r="D52" s="46"/>
+      <c r="E52" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="F52" s="42"/>
+      <c r="F52" s="45"/>
       <c r="G52" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
@@ -5618,16 +5618,16 @@
       </c>
     </row>
     <row r="53" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="42"/>
-      <c r="B53" s="42"/>
-      <c r="C53" s="41" t="s">
+      <c r="A53" s="45"/>
+      <c r="B53" s="45"/>
+      <c r="C53" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="D53" s="41"/>
-      <c r="E53" s="42" t="s">
+      <c r="D53" s="46"/>
+      <c r="E53" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="F53" s="42"/>
+      <c r="F53" s="45"/>
       <c r="G53" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
@@ -5685,16 +5685,16 @@
       </c>
     </row>
     <row r="54" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="42"/>
-      <c r="B54" s="42"/>
-      <c r="C54" s="41" t="s">
+      <c r="A54" s="45"/>
+      <c r="B54" s="45"/>
+      <c r="C54" s="46" t="s">
         <v>165</v>
       </c>
-      <c r="D54" s="41"/>
-      <c r="E54" s="42" t="s">
+      <c r="D54" s="46"/>
+      <c r="E54" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="F54" s="42"/>
+      <c r="F54" s="45"/>
       <c r="G54" s="8">
         <v>2</v>
       </c>
@@ -5751,16 +5751,16 @@
       </c>
     </row>
     <row r="55" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="42"/>
-      <c r="B55" s="40"/>
-      <c r="C55" s="41" t="s">
+      <c r="A55" s="45"/>
+      <c r="B55" s="53"/>
+      <c r="C55" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="41"/>
-      <c r="E55" s="42" t="s">
+      <c r="D55" s="46"/>
+      <c r="E55" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F55" s="42"/>
+      <c r="F55" s="45"/>
       <c r="G55" s="8">
         <f>H55</f>
         <v>5</v>
@@ -5818,18 +5818,18 @@
       </c>
     </row>
     <row r="56" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="42"/>
-      <c r="B56" s="40" t="s">
+      <c r="A56" s="45"/>
+      <c r="B56" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="C56" s="48" t="s">
+      <c r="C56" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="D56" s="49"/>
-      <c r="E56" s="50" t="s">
+      <c r="D56" s="44"/>
+      <c r="E56" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F56" s="51"/>
+      <c r="F56" s="42"/>
       <c r="G56" s="8">
         <f t="shared" si="1"/>
         <v>3</v>
@@ -5887,16 +5887,16 @@
       </c>
     </row>
     <row r="57" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="42"/>
-      <c r="B57" s="42"/>
-      <c r="C57" s="48" t="s">
+      <c r="A57" s="45"/>
+      <c r="B57" s="45"/>
+      <c r="C57" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="D57" s="49"/>
-      <c r="E57" s="50" t="s">
+      <c r="D57" s="44"/>
+      <c r="E57" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="F57" s="51"/>
+      <c r="F57" s="42"/>
       <c r="G57" s="8">
         <f t="shared" ref="G57" si="3">H57</f>
         <v>5</v>
@@ -5954,16 +5954,16 @@
       </c>
     </row>
     <row r="58" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="42"/>
-      <c r="B58" s="42"/>
-      <c r="C58" s="48" t="s">
+      <c r="A58" s="45"/>
+      <c r="B58" s="45"/>
+      <c r="C58" s="43" t="s">
         <v>173</v>
       </c>
-      <c r="D58" s="49"/>
-      <c r="E58" s="50" t="s">
+      <c r="D58" s="44"/>
+      <c r="E58" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F58" s="51"/>
+      <c r="F58" s="42"/>
       <c r="G58" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
@@ -6021,16 +6021,16 @@
       </c>
     </row>
     <row r="59" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="42"/>
-      <c r="B59" s="42"/>
-      <c r="C59" s="48" t="s">
+      <c r="A59" s="45"/>
+      <c r="B59" s="45"/>
+      <c r="C59" s="43" t="s">
         <v>174</v>
       </c>
-      <c r="D59" s="49"/>
-      <c r="E59" s="50" t="s">
+      <c r="D59" s="44"/>
+      <c r="E59" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="F59" s="51"/>
+      <c r="F59" s="42"/>
       <c r="G59" s="8">
         <f t="shared" ref="G59:G102" si="4">H59</f>
         <v>2</v>
@@ -6088,16 +6088,16 @@
       </c>
     </row>
     <row r="60" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="42"/>
-      <c r="B60" s="42"/>
-      <c r="C60" s="48" t="s">
+      <c r="A60" s="45"/>
+      <c r="B60" s="45"/>
+      <c r="C60" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="D60" s="49"/>
-      <c r="E60" s="50" t="s">
+      <c r="D60" s="44"/>
+      <c r="E60" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F60" s="51"/>
+      <c r="F60" s="42"/>
       <c r="G60" s="8">
         <f t="shared" si="4"/>
         <v>3</v>
@@ -6155,16 +6155,16 @@
       </c>
     </row>
     <row r="61" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="42"/>
-      <c r="B61" s="42"/>
-      <c r="C61" s="48" t="s">
+      <c r="A61" s="45"/>
+      <c r="B61" s="45"/>
+      <c r="C61" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="D61" s="49"/>
-      <c r="E61" s="50" t="s">
+      <c r="D61" s="44"/>
+      <c r="E61" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="F61" s="51"/>
+      <c r="F61" s="42"/>
       <c r="G61" s="8">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -6222,16 +6222,16 @@
       </c>
     </row>
     <row r="62" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="42"/>
-      <c r="B62" s="42"/>
-      <c r="C62" s="48" t="s">
+      <c r="A62" s="45"/>
+      <c r="B62" s="45"/>
+      <c r="C62" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="D62" s="49"/>
-      <c r="E62" s="50" t="s">
+      <c r="D62" s="44"/>
+      <c r="E62" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F62" s="51"/>
+      <c r="F62" s="42"/>
       <c r="G62" s="8">
         <f t="shared" si="4"/>
         <v>4</v>
@@ -6289,16 +6289,16 @@
       </c>
     </row>
     <row r="63" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="42"/>
-      <c r="B63" s="42"/>
-      <c r="C63" s="48" t="s">
+      <c r="A63" s="45"/>
+      <c r="B63" s="45"/>
+      <c r="C63" s="43" t="s">
         <v>72</v>
       </c>
-      <c r="D63" s="49"/>
-      <c r="E63" s="50" t="s">
+      <c r="D63" s="44"/>
+      <c r="E63" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="F63" s="51"/>
+      <c r="F63" s="42"/>
       <c r="G63" s="8">
         <f t="shared" si="4"/>
         <v>6</v>
@@ -6356,16 +6356,16 @@
       </c>
     </row>
     <row r="64" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="42"/>
-      <c r="B64" s="42"/>
-      <c r="C64" s="48" t="s">
+      <c r="A64" s="45"/>
+      <c r="B64" s="45"/>
+      <c r="C64" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="D64" s="49"/>
-      <c r="E64" s="50" t="s">
+      <c r="D64" s="44"/>
+      <c r="E64" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F64" s="51"/>
+      <c r="F64" s="42"/>
       <c r="G64" s="8">
         <f t="shared" si="4"/>
         <v>4</v>
@@ -6423,16 +6423,16 @@
       </c>
     </row>
     <row r="65" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="42"/>
-      <c r="B65" s="42"/>
-      <c r="C65" s="48" t="s">
+      <c r="A65" s="45"/>
+      <c r="B65" s="45"/>
+      <c r="C65" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="D65" s="49"/>
-      <c r="E65" s="50" t="s">
+      <c r="D65" s="44"/>
+      <c r="E65" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="F65" s="51"/>
+      <c r="F65" s="42"/>
       <c r="G65" s="8">
         <f t="shared" si="4"/>
         <v>6</v>
@@ -6490,16 +6490,16 @@
       </c>
     </row>
     <row r="66" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="42"/>
-      <c r="B66" s="42"/>
-      <c r="C66" s="48" t="s">
+      <c r="A66" s="45"/>
+      <c r="B66" s="45"/>
+      <c r="C66" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="D66" s="49"/>
-      <c r="E66" s="50" t="s">
+      <c r="D66" s="44"/>
+      <c r="E66" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F66" s="51"/>
+      <c r="F66" s="42"/>
       <c r="G66" s="8">
         <f t="shared" si="4"/>
         <v>3</v>
@@ -6557,16 +6557,16 @@
       </c>
     </row>
     <row r="67" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="42"/>
-      <c r="B67" s="42"/>
-      <c r="C67" s="48" t="s">
+      <c r="A67" s="45"/>
+      <c r="B67" s="45"/>
+      <c r="C67" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D67" s="49"/>
-      <c r="E67" s="50" t="s">
+      <c r="D67" s="44"/>
+      <c r="E67" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="F67" s="51"/>
+      <c r="F67" s="42"/>
       <c r="G67" s="8">
         <f t="shared" si="4"/>
         <v>7</v>
@@ -6624,16 +6624,16 @@
       </c>
     </row>
     <row r="68" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="42"/>
-      <c r="B68" s="42"/>
-      <c r="C68" s="48" t="s">
+      <c r="A68" s="45"/>
+      <c r="B68" s="45"/>
+      <c r="C68" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="D68" s="49"/>
-      <c r="E68" s="50" t="s">
+      <c r="D68" s="44"/>
+      <c r="E68" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F68" s="51"/>
+      <c r="F68" s="42"/>
       <c r="G68" s="8">
         <f t="shared" si="4"/>
         <v>3</v>
@@ -6691,16 +6691,16 @@
       </c>
     </row>
     <row r="69" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="42"/>
-      <c r="B69" s="42"/>
-      <c r="C69" s="48" t="s">
+      <c r="A69" s="45"/>
+      <c r="B69" s="45"/>
+      <c r="C69" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="D69" s="49"/>
-      <c r="E69" s="50" t="s">
+      <c r="D69" s="44"/>
+      <c r="E69" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="F69" s="51"/>
+      <c r="F69" s="42"/>
       <c r="G69" s="8">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -6758,16 +6758,16 @@
       </c>
     </row>
     <row r="70" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="42"/>
-      <c r="B70" s="42"/>
-      <c r="C70" s="48" t="s">
+      <c r="A70" s="45"/>
+      <c r="B70" s="45"/>
+      <c r="C70" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="D70" s="49"/>
-      <c r="E70" s="50" t="s">
+      <c r="D70" s="44"/>
+      <c r="E70" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F70" s="51"/>
+      <c r="F70" s="42"/>
       <c r="G70" s="8">
         <f t="shared" si="4"/>
         <v>3</v>
@@ -6825,16 +6825,16 @@
       </c>
     </row>
     <row r="71" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="42"/>
-      <c r="B71" s="42"/>
-      <c r="C71" s="48" t="s">
+      <c r="A71" s="45"/>
+      <c r="B71" s="45"/>
+      <c r="C71" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="D71" s="49"/>
-      <c r="E71" s="50" t="s">
+      <c r="D71" s="44"/>
+      <c r="E71" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="F71" s="51"/>
+      <c r="F71" s="42"/>
       <c r="G71" s="8">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -6892,16 +6892,16 @@
       </c>
     </row>
     <row r="72" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="42"/>
-      <c r="B72" s="42"/>
-      <c r="C72" s="48" t="s">
+      <c r="A72" s="45"/>
+      <c r="B72" s="45"/>
+      <c r="C72" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="D72" s="49"/>
-      <c r="E72" s="50" t="s">
+      <c r="D72" s="44"/>
+      <c r="E72" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F72" s="51"/>
+      <c r="F72" s="42"/>
       <c r="G72" s="8">
         <f t="shared" si="4"/>
         <v>2</v>
@@ -6959,16 +6959,16 @@
       </c>
     </row>
     <row r="73" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="42"/>
-      <c r="B73" s="42"/>
-      <c r="C73" s="48" t="s">
+      <c r="A73" s="45"/>
+      <c r="B73" s="45"/>
+      <c r="C73" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="D73" s="49"/>
-      <c r="E73" s="50" t="s">
+      <c r="D73" s="44"/>
+      <c r="E73" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F73" s="51"/>
+      <c r="F73" s="42"/>
       <c r="G73" s="8">
         <f t="shared" si="4"/>
         <v>6</v>
@@ -7026,16 +7026,16 @@
       </c>
     </row>
     <row r="74" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="42"/>
-      <c r="B74" s="42"/>
-      <c r="C74" s="48" t="s">
+      <c r="A74" s="45"/>
+      <c r="B74" s="45"/>
+      <c r="C74" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="D74" s="49"/>
-      <c r="E74" s="50" t="s">
+      <c r="D74" s="44"/>
+      <c r="E74" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F74" s="51"/>
+      <c r="F74" s="42"/>
       <c r="G74" s="8">
         <f t="shared" si="4"/>
         <v>2</v>
@@ -7093,16 +7093,16 @@
       </c>
     </row>
     <row r="75" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="42"/>
-      <c r="B75" s="42"/>
-      <c r="C75" s="48" t="s">
+      <c r="A75" s="45"/>
+      <c r="B75" s="45"/>
+      <c r="C75" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="D75" s="49"/>
-      <c r="E75" s="50" t="s">
+      <c r="D75" s="44"/>
+      <c r="E75" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F75" s="51"/>
+      <c r="F75" s="42"/>
       <c r="G75" s="8">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -7160,16 +7160,16 @@
       </c>
     </row>
     <row r="76" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="42"/>
-      <c r="B76" s="42"/>
-      <c r="C76" s="48" t="s">
+      <c r="A76" s="45"/>
+      <c r="B76" s="45"/>
+      <c r="C76" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="D76" s="49"/>
-      <c r="E76" s="50" t="s">
+      <c r="D76" s="44"/>
+      <c r="E76" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F76" s="51"/>
+      <c r="F76" s="42"/>
       <c r="G76" s="8">
         <f t="shared" si="4"/>
         <v>3</v>
@@ -7227,16 +7227,16 @@
       </c>
     </row>
     <row r="77" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="42"/>
-      <c r="B77" s="42"/>
-      <c r="C77" s="48" t="s">
+      <c r="A77" s="45"/>
+      <c r="B77" s="45"/>
+      <c r="C77" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="D77" s="49"/>
-      <c r="E77" s="50" t="s">
+      <c r="D77" s="44"/>
+      <c r="E77" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="F77" s="51"/>
+      <c r="F77" s="42"/>
       <c r="G77" s="8">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -7294,16 +7294,16 @@
       </c>
     </row>
     <row r="78" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="42"/>
-      <c r="B78" s="42"/>
-      <c r="C78" s="48" t="s">
+      <c r="A78" s="45"/>
+      <c r="B78" s="45"/>
+      <c r="C78" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="D78" s="49"/>
-      <c r="E78" s="50" t="s">
+      <c r="D78" s="44"/>
+      <c r="E78" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F78" s="51"/>
+      <c r="F78" s="42"/>
       <c r="G78" s="8">
         <f t="shared" si="4"/>
         <v>3</v>
@@ -7361,16 +7361,16 @@
       </c>
     </row>
     <row r="79" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="42"/>
-      <c r="B79" s="42"/>
-      <c r="C79" s="48" t="s">
+      <c r="A79" s="45"/>
+      <c r="B79" s="45"/>
+      <c r="C79" s="43" t="s">
         <v>176</v>
       </c>
-      <c r="D79" s="49"/>
-      <c r="E79" s="50" t="s">
+      <c r="D79" s="44"/>
+      <c r="E79" s="41" t="s">
         <v>147</v>
       </c>
-      <c r="F79" s="51"/>
+      <c r="F79" s="42"/>
       <c r="G79" s="8">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -7428,16 +7428,16 @@
       </c>
     </row>
     <row r="80" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="42"/>
-      <c r="B80" s="42"/>
-      <c r="C80" s="48" t="s">
+      <c r="A80" s="45"/>
+      <c r="B80" s="45"/>
+      <c r="C80" s="43" t="s">
         <v>177</v>
       </c>
-      <c r="D80" s="49"/>
-      <c r="E80" s="50" t="s">
+      <c r="D80" s="44"/>
+      <c r="E80" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F80" s="51"/>
+      <c r="F80" s="42"/>
       <c r="G80" s="8">
         <v>2</v>
       </c>
@@ -7494,16 +7494,16 @@
       </c>
     </row>
     <row r="81" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="42"/>
-      <c r="B81" s="42"/>
-      <c r="C81" s="48" t="s">
+      <c r="A81" s="45"/>
+      <c r="B81" s="45"/>
+      <c r="C81" s="43" t="s">
         <v>178</v>
       </c>
-      <c r="D81" s="49"/>
-      <c r="E81" s="50" t="s">
+      <c r="D81" s="44"/>
+      <c r="E81" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F81" s="51"/>
+      <c r="F81" s="42"/>
       <c r="G81" s="8">
         <v>4</v>
       </c>
@@ -7560,16 +7560,16 @@
       </c>
     </row>
     <row r="82" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="42"/>
-      <c r="B82" s="42"/>
-      <c r="C82" s="48" t="s">
+      <c r="A82" s="45"/>
+      <c r="B82" s="45"/>
+      <c r="C82" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="D82" s="49"/>
-      <c r="E82" s="50" t="s">
+      <c r="D82" s="44"/>
+      <c r="E82" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F82" s="51"/>
+      <c r="F82" s="42"/>
       <c r="G82" s="8">
         <v>3</v>
       </c>
@@ -7626,16 +7626,16 @@
       </c>
     </row>
     <row r="83" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="42"/>
-      <c r="B83" s="42"/>
-      <c r="C83" s="48" t="s">
+      <c r="A83" s="45"/>
+      <c r="B83" s="45"/>
+      <c r="C83" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="D83" s="49"/>
-      <c r="E83" s="50" t="s">
+      <c r="D83" s="44"/>
+      <c r="E83" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="F83" s="51"/>
+      <c r="F83" s="42"/>
       <c r="G83" s="8">
         <v>10</v>
       </c>
@@ -7692,12 +7692,12 @@
       </c>
     </row>
     <row r="84" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="42"/>
-      <c r="B84" s="42"/>
-      <c r="C84" s="50"/>
-      <c r="D84" s="51"/>
-      <c r="E84" s="50"/>
-      <c r="F84" s="51"/>
+      <c r="A84" s="45"/>
+      <c r="B84" s="45"/>
+      <c r="C84" s="41"/>
+      <c r="D84" s="42"/>
+      <c r="E84" s="41"/>
+      <c r="F84" s="42"/>
       <c r="G84" s="8"/>
       <c r="H84" s="33"/>
       <c r="I84" s="33"/>
@@ -7720,16 +7720,16 @@
       <c r="X84" s="8"/>
     </row>
     <row r="85" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="42"/>
-      <c r="B85" s="42"/>
-      <c r="C85" s="48" t="s">
+      <c r="A85" s="45"/>
+      <c r="B85" s="45"/>
+      <c r="C85" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="D85" s="49"/>
-      <c r="E85" s="50" t="s">
+      <c r="D85" s="44"/>
+      <c r="E85" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F85" s="51"/>
+      <c r="F85" s="42"/>
       <c r="G85" s="8">
         <v>2</v>
       </c>
@@ -7786,16 +7786,16 @@
       </c>
     </row>
     <row r="86" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="42"/>
-      <c r="B86" s="42"/>
-      <c r="C86" s="48" t="s">
+      <c r="A86" s="45"/>
+      <c r="B86" s="45"/>
+      <c r="C86" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="D86" s="49"/>
-      <c r="E86" s="50" t="s">
+      <c r="D86" s="44"/>
+      <c r="E86" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="F86" s="51"/>
+      <c r="F86" s="42"/>
       <c r="G86" s="8">
         <v>8</v>
       </c>
@@ -7852,12 +7852,12 @@
       </c>
     </row>
     <row r="87" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="42"/>
-      <c r="B87" s="42"/>
-      <c r="C87" s="50"/>
-      <c r="D87" s="51"/>
-      <c r="E87" s="50"/>
-      <c r="F87" s="51"/>
+      <c r="A87" s="45"/>
+      <c r="B87" s="45"/>
+      <c r="C87" s="41"/>
+      <c r="D87" s="42"/>
+      <c r="E87" s="41"/>
+      <c r="F87" s="42"/>
       <c r="G87" s="8"/>
       <c r="H87" s="33"/>
       <c r="I87" s="33"/>
@@ -7880,16 +7880,16 @@
       </c>
     </row>
     <row r="88" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="42"/>
-      <c r="B88" s="42"/>
-      <c r="C88" s="48" t="s">
+      <c r="A88" s="45"/>
+      <c r="B88" s="45"/>
+      <c r="C88" s="43" t="s">
         <v>179</v>
       </c>
-      <c r="D88" s="49"/>
-      <c r="E88" s="50" t="s">
+      <c r="D88" s="44"/>
+      <c r="E88" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F88" s="51"/>
+      <c r="F88" s="42"/>
       <c r="G88" s="8">
         <v>3</v>
       </c>
@@ -7946,16 +7946,16 @@
       </c>
     </row>
     <row r="89" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="42"/>
-      <c r="B89" s="42"/>
-      <c r="C89" s="48" t="s">
+      <c r="A89" s="45"/>
+      <c r="B89" s="45"/>
+      <c r="C89" s="43" t="s">
         <v>180</v>
       </c>
-      <c r="D89" s="49"/>
-      <c r="E89" s="50" t="s">
+      <c r="D89" s="44"/>
+      <c r="E89" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="F89" s="51"/>
+      <c r="F89" s="42"/>
       <c r="G89" s="8">
         <v>8</v>
       </c>
@@ -8012,12 +8012,12 @@
       </c>
     </row>
     <row r="90" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="42"/>
-      <c r="B90" s="42"/>
-      <c r="C90" s="50"/>
-      <c r="D90" s="51"/>
-      <c r="E90" s="50"/>
-      <c r="F90" s="51"/>
+      <c r="A90" s="45"/>
+      <c r="B90" s="45"/>
+      <c r="C90" s="41"/>
+      <c r="D90" s="42"/>
+      <c r="E90" s="41"/>
+      <c r="F90" s="42"/>
       <c r="G90" s="8"/>
       <c r="H90" s="33"/>
       <c r="I90" s="33"/>
@@ -8040,16 +8040,16 @@
       </c>
     </row>
     <row r="91" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="42"/>
-      <c r="B91" s="40"/>
-      <c r="C91" s="41" t="s">
+      <c r="A91" s="45"/>
+      <c r="B91" s="53"/>
+      <c r="C91" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="D91" s="41"/>
-      <c r="E91" s="42" t="s">
+      <c r="D91" s="46"/>
+      <c r="E91" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F91" s="42"/>
+      <c r="F91" s="45"/>
       <c r="G91" s="8">
         <f t="shared" si="4"/>
         <v>10</v>
@@ -8107,18 +8107,18 @@
       </c>
     </row>
     <row r="92" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="42"/>
-      <c r="B92" s="40" t="s">
+      <c r="A92" s="45"/>
+      <c r="B92" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="C92" s="41" t="s">
+      <c r="C92" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="D92" s="41"/>
-      <c r="E92" s="50" t="s">
+      <c r="D92" s="46"/>
+      <c r="E92" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F92" s="51"/>
+      <c r="F92" s="42"/>
       <c r="G92" s="8">
         <f>H92</f>
         <v>2</v>
@@ -8176,16 +8176,16 @@
       </c>
     </row>
     <row r="93" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="42"/>
-      <c r="B93" s="40"/>
-      <c r="C93" s="41" t="s">
+      <c r="A93" s="45"/>
+      <c r="B93" s="53"/>
+      <c r="C93" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="D93" s="41"/>
-      <c r="E93" s="50" t="s">
+      <c r="D93" s="46"/>
+      <c r="E93" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F93" s="51"/>
+      <c r="F93" s="42"/>
       <c r="G93" s="8">
         <f t="shared" ref="G93" si="5">H93</f>
         <v>1</v>
@@ -8243,16 +8243,16 @@
       </c>
     </row>
     <row r="94" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="42"/>
-      <c r="B94" s="42"/>
-      <c r="C94" s="41" t="s">
+      <c r="A94" s="45"/>
+      <c r="B94" s="45"/>
+      <c r="C94" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="D94" s="41"/>
-      <c r="E94" s="50" t="s">
+      <c r="D94" s="46"/>
+      <c r="E94" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F94" s="51"/>
+      <c r="F94" s="42"/>
       <c r="G94" s="8">
         <f t="shared" si="4"/>
         <v>2</v>
@@ -8310,16 +8310,16 @@
       </c>
     </row>
     <row r="95" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="42"/>
-      <c r="B95" s="42"/>
-      <c r="C95" s="41" t="s">
+      <c r="A95" s="45"/>
+      <c r="B95" s="45"/>
+      <c r="C95" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="D95" s="41"/>
-      <c r="E95" s="50" t="s">
+      <c r="D95" s="46"/>
+      <c r="E95" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F95" s="51"/>
+      <c r="F95" s="42"/>
       <c r="G95" s="8">
         <f>H95</f>
         <v>2</v>
@@ -8377,16 +8377,16 @@
       </c>
     </row>
     <row r="96" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="42"/>
-      <c r="B96" s="42"/>
-      <c r="C96" s="41" t="s">
+      <c r="A96" s="45"/>
+      <c r="B96" s="45"/>
+      <c r="C96" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="D96" s="41"/>
-      <c r="E96" s="50" t="s">
+      <c r="D96" s="46"/>
+      <c r="E96" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F96" s="51"/>
+      <c r="F96" s="42"/>
       <c r="G96" s="8">
         <f t="shared" si="4"/>
         <v>3</v>
@@ -8444,16 +8444,16 @@
       </c>
     </row>
     <row r="97" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="42"/>
-      <c r="B97" s="42"/>
-      <c r="C97" s="41" t="s">
+      <c r="A97" s="45"/>
+      <c r="B97" s="45"/>
+      <c r="C97" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="D97" s="41"/>
-      <c r="E97" s="50" t="s">
+      <c r="D97" s="46"/>
+      <c r="E97" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F97" s="51"/>
+      <c r="F97" s="42"/>
       <c r="G97" s="8">
         <f t="shared" si="4"/>
         <v>2</v>
@@ -8511,16 +8511,16 @@
       </c>
     </row>
     <row r="98" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="42"/>
-      <c r="B98" s="42"/>
-      <c r="C98" s="41" t="s">
+      <c r="A98" s="45"/>
+      <c r="B98" s="45"/>
+      <c r="C98" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="41"/>
-      <c r="E98" s="50" t="s">
+      <c r="D98" s="46"/>
+      <c r="E98" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F98" s="51"/>
+      <c r="F98" s="42"/>
       <c r="G98" s="8">
         <f t="shared" si="4"/>
         <v>2</v>
@@ -8578,16 +8578,16 @@
       </c>
     </row>
     <row r="99" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="42"/>
-      <c r="B99" s="42"/>
-      <c r="C99" s="41" t="s">
+      <c r="A99" s="45"/>
+      <c r="B99" s="45"/>
+      <c r="C99" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="D99" s="41"/>
-      <c r="E99" s="50" t="s">
+      <c r="D99" s="46"/>
+      <c r="E99" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F99" s="51"/>
+      <c r="F99" s="42"/>
       <c r="G99" s="8">
         <f t="shared" si="4"/>
         <v>2</v>
@@ -8645,16 +8645,16 @@
       </c>
     </row>
     <row r="100" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="42"/>
-      <c r="B100" s="42"/>
-      <c r="C100" s="41" t="s">
+      <c r="A100" s="45"/>
+      <c r="B100" s="45"/>
+      <c r="C100" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="D100" s="41"/>
-      <c r="E100" s="50" t="s">
+      <c r="D100" s="46"/>
+      <c r="E100" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F100" s="51"/>
+      <c r="F100" s="42"/>
       <c r="G100" s="8">
         <f t="shared" si="4"/>
         <v>2</v>
@@ -8712,16 +8712,16 @@
       </c>
     </row>
     <row r="101" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="42"/>
-      <c r="B101" s="42"/>
-      <c r="C101" s="41" t="s">
+      <c r="A101" s="45"/>
+      <c r="B101" s="45"/>
+      <c r="C101" s="46" t="s">
         <v>172</v>
       </c>
-      <c r="D101" s="41"/>
-      <c r="E101" s="50" t="s">
+      <c r="D101" s="46"/>
+      <c r="E101" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F101" s="51"/>
+      <c r="F101" s="42"/>
       <c r="G101" s="8">
         <f t="shared" si="4"/>
         <v>4</v>
@@ -8779,16 +8779,16 @@
       </c>
     </row>
     <row r="102" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="42"/>
-      <c r="B102" s="42"/>
-      <c r="C102" s="41" t="s">
+      <c r="A102" s="45"/>
+      <c r="B102" s="45"/>
+      <c r="C102" s="46" t="s">
         <v>171</v>
       </c>
-      <c r="D102" s="41"/>
-      <c r="E102" s="50" t="s">
+      <c r="D102" s="46"/>
+      <c r="E102" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F102" s="51"/>
+      <c r="F102" s="42"/>
       <c r="G102" s="8">
         <f t="shared" si="4"/>
         <v>2</v>
@@ -8846,16 +8846,16 @@
       </c>
     </row>
     <row r="103" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="42"/>
-      <c r="B103" s="42"/>
-      <c r="C103" s="41" t="s">
+      <c r="A103" s="45"/>
+      <c r="B103" s="45"/>
+      <c r="C103" s="46" t="s">
         <v>170</v>
       </c>
-      <c r="D103" s="41"/>
-      <c r="E103" s="50" t="s">
+      <c r="D103" s="46"/>
+      <c r="E103" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F103" s="51"/>
+      <c r="F103" s="42"/>
       <c r="G103" s="8">
         <f t="shared" ref="G103:G141" si="6">H103</f>
         <v>2</v>
@@ -8913,16 +8913,16 @@
       </c>
     </row>
     <row r="104" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="42"/>
-      <c r="B104" s="42"/>
-      <c r="C104" s="41" t="s">
+      <c r="A104" s="45"/>
+      <c r="B104" s="45"/>
+      <c r="C104" s="46" t="s">
         <v>169</v>
       </c>
-      <c r="D104" s="41"/>
-      <c r="E104" s="50" t="s">
+      <c r="D104" s="46"/>
+      <c r="E104" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F104" s="51"/>
+      <c r="F104" s="42"/>
       <c r="G104" s="8">
         <v>1</v>
       </c>
@@ -8979,16 +8979,16 @@
       </c>
     </row>
     <row r="105" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="42"/>
-      <c r="B105" s="42"/>
-      <c r="C105" s="41" t="s">
+      <c r="A105" s="45"/>
+      <c r="B105" s="45"/>
+      <c r="C105" s="46" t="s">
         <v>168</v>
       </c>
-      <c r="D105" s="41"/>
-      <c r="E105" s="50" t="s">
+      <c r="D105" s="46"/>
+      <c r="E105" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="F105" s="51"/>
+      <c r="F105" s="42"/>
       <c r="G105" s="8">
         <v>2</v>
       </c>
@@ -9045,16 +9045,16 @@
       </c>
     </row>
     <row r="106" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="42"/>
-      <c r="B106" s="42"/>
-      <c r="C106" s="41" t="s">
+      <c r="A106" s="45"/>
+      <c r="B106" s="45"/>
+      <c r="C106" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="D106" s="41"/>
-      <c r="E106" s="50" t="s">
+      <c r="D106" s="46"/>
+      <c r="E106" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="F106" s="51"/>
+      <c r="F106" s="42"/>
       <c r="G106" s="8">
         <v>1</v>
       </c>
@@ -9111,16 +9111,16 @@
       </c>
     </row>
     <row r="107" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="42"/>
-      <c r="B107" s="40"/>
-      <c r="C107" s="41" t="s">
+      <c r="A107" s="45"/>
+      <c r="B107" s="53"/>
+      <c r="C107" s="46" t="s">
         <v>167</v>
       </c>
-      <c r="D107" s="41"/>
-      <c r="E107" s="50" t="s">
+      <c r="D107" s="46"/>
+      <c r="E107" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="F107" s="51"/>
+      <c r="F107" s="42"/>
       <c r="G107" s="8">
         <f t="shared" si="6"/>
         <v>2</v>
@@ -9178,18 +9178,18 @@
       </c>
     </row>
     <row r="108" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="42"/>
-      <c r="B108" s="40" t="s">
+      <c r="A108" s="45"/>
+      <c r="B108" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="C108" s="48" t="s">
+      <c r="C108" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="D108" s="49"/>
-      <c r="E108" s="42" t="s">
+      <c r="D108" s="44"/>
+      <c r="E108" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F108" s="42"/>
+      <c r="F108" s="45"/>
       <c r="G108" s="33">
         <v>2</v>
       </c>
@@ -9246,16 +9246,16 @@
       </c>
     </row>
     <row r="109" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="42"/>
-      <c r="B109" s="42"/>
-      <c r="C109" s="48" t="s">
+      <c r="A109" s="45"/>
+      <c r="B109" s="45"/>
+      <c r="C109" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="D109" s="49"/>
-      <c r="E109" s="42" t="s">
+      <c r="D109" s="44"/>
+      <c r="E109" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F109" s="42"/>
+      <c r="F109" s="45"/>
       <c r="G109" s="33">
         <v>0</v>
       </c>
@@ -9312,16 +9312,16 @@
       </c>
     </row>
     <row r="110" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="42"/>
-      <c r="B110" s="42"/>
-      <c r="C110" s="48" t="s">
+      <c r="A110" s="45"/>
+      <c r="B110" s="45"/>
+      <c r="C110" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="D110" s="49"/>
-      <c r="E110" s="42" t="s">
+      <c r="D110" s="44"/>
+      <c r="E110" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F110" s="42"/>
+      <c r="F110" s="45"/>
       <c r="G110" s="33">
         <v>0</v>
       </c>
@@ -9378,16 +9378,16 @@
       </c>
     </row>
     <row r="111" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="42"/>
-      <c r="B111" s="42"/>
-      <c r="C111" s="48" t="s">
+      <c r="A111" s="45"/>
+      <c r="B111" s="45"/>
+      <c r="C111" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="D111" s="49"/>
-      <c r="E111" s="42" t="s">
+      <c r="D111" s="44"/>
+      <c r="E111" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F111" s="42"/>
+      <c r="F111" s="45"/>
       <c r="G111" s="33">
         <v>0</v>
       </c>
@@ -9444,16 +9444,16 @@
       </c>
     </row>
     <row r="112" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="42"/>
-      <c r="B112" s="42"/>
-      <c r="C112" s="48" t="s">
+      <c r="A112" s="45"/>
+      <c r="B112" s="45"/>
+      <c r="C112" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="D112" s="49"/>
-      <c r="E112" s="42" t="s">
+      <c r="D112" s="44"/>
+      <c r="E112" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F112" s="42"/>
+      <c r="F112" s="45"/>
       <c r="G112" s="33">
         <v>0</v>
       </c>
@@ -9510,16 +9510,16 @@
       </c>
     </row>
     <row r="113" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="42"/>
-      <c r="B113" s="42"/>
-      <c r="C113" s="48" t="s">
+      <c r="A113" s="45"/>
+      <c r="B113" s="45"/>
+      <c r="C113" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="D113" s="49"/>
-      <c r="E113" s="42" t="s">
+      <c r="D113" s="44"/>
+      <c r="E113" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F113" s="42"/>
+      <c r="F113" s="45"/>
       <c r="G113" s="33">
         <v>0</v>
       </c>
@@ -9576,16 +9576,16 @@
       </c>
     </row>
     <row r="114" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="42"/>
-      <c r="B114" s="42"/>
-      <c r="C114" s="48" t="s">
+      <c r="A114" s="45"/>
+      <c r="B114" s="45"/>
+      <c r="C114" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="D114" s="49"/>
-      <c r="E114" s="42" t="s">
+      <c r="D114" s="44"/>
+      <c r="E114" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F114" s="42"/>
+      <c r="F114" s="45"/>
       <c r="G114" s="33">
         <v>0</v>
       </c>
@@ -9642,16 +9642,16 @@
       </c>
     </row>
     <row r="115" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="42"/>
-      <c r="B115" s="42"/>
-      <c r="C115" s="48" t="s">
+      <c r="A115" s="45"/>
+      <c r="B115" s="45"/>
+      <c r="C115" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="D115" s="49"/>
-      <c r="E115" s="42" t="s">
+      <c r="D115" s="44"/>
+      <c r="E115" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F115" s="42"/>
+      <c r="F115" s="45"/>
       <c r="G115" s="33">
         <v>0</v>
       </c>
@@ -9708,16 +9708,16 @@
       </c>
     </row>
     <row r="116" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="42"/>
-      <c r="B116" s="42"/>
-      <c r="C116" s="48" t="s">
+      <c r="A116" s="45"/>
+      <c r="B116" s="45"/>
+      <c r="C116" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="D116" s="49"/>
-      <c r="E116" s="42" t="s">
+      <c r="D116" s="44"/>
+      <c r="E116" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F116" s="42"/>
+      <c r="F116" s="45"/>
       <c r="G116" s="33">
         <v>0</v>
       </c>
@@ -9774,16 +9774,16 @@
       </c>
     </row>
     <row r="117" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="42"/>
-      <c r="B117" s="42"/>
-      <c r="C117" s="48" t="s">
+      <c r="A117" s="45"/>
+      <c r="B117" s="45"/>
+      <c r="C117" s="43" t="s">
         <v>111</v>
       </c>
-      <c r="D117" s="49"/>
-      <c r="E117" s="42" t="s">
+      <c r="D117" s="44"/>
+      <c r="E117" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F117" s="42"/>
+      <c r="F117" s="45"/>
       <c r="G117" s="33">
         <v>0</v>
       </c>
@@ -9840,16 +9840,16 @@
       </c>
     </row>
     <row r="118" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A118" s="42"/>
-      <c r="B118" s="42"/>
-      <c r="C118" s="48" t="s">
+      <c r="A118" s="45"/>
+      <c r="B118" s="45"/>
+      <c r="C118" s="43" t="s">
         <v>112</v>
       </c>
-      <c r="D118" s="49"/>
-      <c r="E118" s="42" t="s">
+      <c r="D118" s="44"/>
+      <c r="E118" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F118" s="42"/>
+      <c r="F118" s="45"/>
       <c r="G118" s="33">
         <v>0</v>
       </c>
@@ -9906,16 +9906,16 @@
       </c>
     </row>
     <row r="119" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="42"/>
-      <c r="B119" s="42"/>
-      <c r="C119" s="48" t="s">
+      <c r="A119" s="45"/>
+      <c r="B119" s="45"/>
+      <c r="C119" s="43" t="s">
         <v>182</v>
       </c>
-      <c r="D119" s="49"/>
-      <c r="E119" s="42" t="s">
+      <c r="D119" s="44"/>
+      <c r="E119" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F119" s="42"/>
+      <c r="F119" s="45"/>
       <c r="G119" s="33">
         <v>0</v>
       </c>
@@ -9972,16 +9972,16 @@
       </c>
     </row>
     <row r="120" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="42"/>
-      <c r="B120" s="42"/>
-      <c r="C120" s="48" t="s">
+      <c r="A120" s="45"/>
+      <c r="B120" s="45"/>
+      <c r="C120" s="43" t="s">
         <v>183</v>
       </c>
-      <c r="D120" s="49"/>
-      <c r="E120" s="42" t="s">
+      <c r="D120" s="44"/>
+      <c r="E120" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F120" s="42"/>
+      <c r="F120" s="45"/>
       <c r="G120" s="33">
         <v>0</v>
       </c>
@@ -10038,16 +10038,16 @@
       </c>
     </row>
     <row r="121" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="42"/>
-      <c r="B121" s="42"/>
-      <c r="C121" s="48" t="s">
+      <c r="A121" s="45"/>
+      <c r="B121" s="45"/>
+      <c r="C121" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="D121" s="49"/>
-      <c r="E121" s="42" t="s">
+      <c r="D121" s="44"/>
+      <c r="E121" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F121" s="42"/>
+      <c r="F121" s="45"/>
       <c r="G121" s="33">
         <v>0</v>
       </c>
@@ -10104,16 +10104,16 @@
       </c>
     </row>
     <row r="122" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A122" s="42"/>
-      <c r="B122" s="42"/>
-      <c r="C122" s="48" t="s">
+      <c r="A122" s="45"/>
+      <c r="B122" s="45"/>
+      <c r="C122" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="D122" s="49"/>
-      <c r="E122" s="42" t="s">
+      <c r="D122" s="44"/>
+      <c r="E122" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F122" s="42"/>
+      <c r="F122" s="45"/>
       <c r="G122" s="33">
         <v>1</v>
       </c>
@@ -10170,16 +10170,16 @@
       </c>
     </row>
     <row r="123" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="42"/>
-      <c r="B123" s="40"/>
-      <c r="C123" s="48" t="s">
+      <c r="A123" s="45"/>
+      <c r="B123" s="53"/>
+      <c r="C123" s="43" t="s">
         <v>184</v>
       </c>
-      <c r="D123" s="49"/>
-      <c r="E123" s="42" t="s">
+      <c r="D123" s="44"/>
+      <c r="E123" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F123" s="42"/>
+      <c r="F123" s="45"/>
       <c r="G123" s="33">
         <v>0</v>
       </c>
@@ -10236,18 +10236,18 @@
       </c>
     </row>
     <row r="124" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="42"/>
-      <c r="B124" s="40" t="s">
+      <c r="A124" s="45"/>
+      <c r="B124" s="53" t="s">
         <v>115</v>
       </c>
-      <c r="C124" s="46" t="s">
+      <c r="C124" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="D124" s="46"/>
-      <c r="E124" s="47" t="s">
+      <c r="D124" s="40"/>
+      <c r="E124" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="F124" s="47"/>
+      <c r="F124" s="54"/>
       <c r="G124" s="8">
         <f t="shared" si="6"/>
         <v>2</v>
@@ -10305,16 +10305,16 @@
       </c>
     </row>
     <row r="125" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A125" s="42"/>
-      <c r="B125" s="42"/>
-      <c r="C125" s="46" t="s">
+      <c r="A125" s="45"/>
+      <c r="B125" s="45"/>
+      <c r="C125" s="40" t="s">
         <v>185</v>
       </c>
-      <c r="D125" s="46"/>
-      <c r="E125" s="47" t="s">
+      <c r="D125" s="40"/>
+      <c r="E125" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="F125" s="47"/>
+      <c r="F125" s="54"/>
       <c r="G125" s="8">
         <f t="shared" si="6"/>
         <v>2</v>
@@ -10372,16 +10372,16 @@
       </c>
     </row>
     <row r="126" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="42"/>
-      <c r="B126" s="42"/>
-      <c r="C126" s="46" t="s">
+      <c r="A126" s="45"/>
+      <c r="B126" s="45"/>
+      <c r="C126" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="D126" s="46"/>
-      <c r="E126" s="47" t="s">
+      <c r="D126" s="40"/>
+      <c r="E126" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="F126" s="47"/>
+      <c r="F126" s="54"/>
       <c r="G126" s="8">
         <f t="shared" si="6"/>
         <v>2</v>
@@ -10439,16 +10439,16 @@
       </c>
     </row>
     <row r="127" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="42"/>
-      <c r="B127" s="42"/>
-      <c r="C127" s="46" t="s">
+      <c r="A127" s="45"/>
+      <c r="B127" s="45"/>
+      <c r="C127" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="D127" s="46"/>
-      <c r="E127" s="47" t="s">
+      <c r="D127" s="40"/>
+      <c r="E127" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="F127" s="47"/>
+      <c r="F127" s="54"/>
       <c r="G127" s="8">
         <f t="shared" si="6"/>
         <v>2</v>
@@ -10506,16 +10506,16 @@
       </c>
     </row>
     <row r="128" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="42"/>
-      <c r="B128" s="42"/>
-      <c r="C128" s="46" t="s">
+      <c r="A128" s="45"/>
+      <c r="B128" s="45"/>
+      <c r="C128" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="D128" s="46"/>
-      <c r="E128" s="47" t="s">
+      <c r="D128" s="40"/>
+      <c r="E128" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="F128" s="47"/>
+      <c r="F128" s="54"/>
       <c r="G128" s="8">
         <f t="shared" si="6"/>
         <v>2</v>
@@ -10573,16 +10573,16 @@
       </c>
     </row>
     <row r="129" spans="1:32" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A129" s="42"/>
-      <c r="B129" s="42"/>
-      <c r="C129" s="46" t="s">
+      <c r="A129" s="45"/>
+      <c r="B129" s="45"/>
+      <c r="C129" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="D129" s="46"/>
-      <c r="E129" s="47" t="s">
+      <c r="D129" s="40"/>
+      <c r="E129" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="F129" s="47"/>
+      <c r="F129" s="54"/>
       <c r="G129" s="8">
         <f t="shared" si="6"/>
         <v>2</v>
@@ -10640,16 +10640,16 @@
       </c>
     </row>
     <row r="130" spans="1:32" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A130" s="42"/>
-      <c r="B130" s="42"/>
-      <c r="C130" s="46" t="s">
+      <c r="A130" s="45"/>
+      <c r="B130" s="45"/>
+      <c r="C130" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="D130" s="46"/>
-      <c r="E130" s="47" t="s">
+      <c r="D130" s="40"/>
+      <c r="E130" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="F130" s="47"/>
+      <c r="F130" s="54"/>
       <c r="G130" s="8">
         <f t="shared" si="6"/>
         <v>2</v>
@@ -10707,16 +10707,16 @@
       </c>
     </row>
     <row r="131" spans="1:32" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="42"/>
-      <c r="B131" s="42"/>
-      <c r="C131" s="46" t="s">
+      <c r="A131" s="45"/>
+      <c r="B131" s="45"/>
+      <c r="C131" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="D131" s="46"/>
-      <c r="E131" s="47" t="s">
+      <c r="D131" s="40"/>
+      <c r="E131" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="F131" s="47"/>
+      <c r="F131" s="54"/>
       <c r="G131" s="8">
         <f t="shared" si="6"/>
         <v>2</v>
@@ -10774,16 +10774,16 @@
       </c>
     </row>
     <row r="132" spans="1:32" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A132" s="42"/>
-      <c r="B132" s="42"/>
-      <c r="C132" s="46" t="s">
+      <c r="A132" s="45"/>
+      <c r="B132" s="45"/>
+      <c r="C132" s="40" t="s">
         <v>123</v>
       </c>
-      <c r="D132" s="46"/>
-      <c r="E132" s="47" t="s">
+      <c r="D132" s="40"/>
+      <c r="E132" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="F132" s="47"/>
+      <c r="F132" s="54"/>
       <c r="G132" s="8">
         <f t="shared" si="6"/>
         <v>2</v>
@@ -10841,16 +10841,16 @@
       </c>
     </row>
     <row r="133" spans="1:32" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="42"/>
-      <c r="B133" s="42"/>
-      <c r="C133" s="46" t="s">
+      <c r="A133" s="45"/>
+      <c r="B133" s="45"/>
+      <c r="C133" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="D133" s="46"/>
-      <c r="E133" s="47" t="s">
+      <c r="D133" s="40"/>
+      <c r="E133" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="F133" s="47"/>
+      <c r="F133" s="54"/>
       <c r="G133" s="8">
         <f t="shared" si="6"/>
         <v>3</v>
@@ -10908,16 +10908,16 @@
       </c>
     </row>
     <row r="134" spans="1:32" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A134" s="42"/>
-      <c r="B134" s="42"/>
-      <c r="C134" s="46" t="s">
+      <c r="A134" s="45"/>
+      <c r="B134" s="45"/>
+      <c r="C134" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="D134" s="46"/>
-      <c r="E134" s="47" t="s">
+      <c r="D134" s="40"/>
+      <c r="E134" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="F134" s="47"/>
+      <c r="F134" s="54"/>
       <c r="G134" s="8">
         <f t="shared" si="6"/>
         <v>2</v>
@@ -10975,16 +10975,16 @@
       </c>
     </row>
     <row r="135" spans="1:32" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A135" s="42"/>
-      <c r="B135" s="42"/>
-      <c r="C135" s="46" t="s">
+      <c r="A135" s="45"/>
+      <c r="B135" s="45"/>
+      <c r="C135" s="40" t="s">
         <v>186</v>
       </c>
-      <c r="D135" s="46"/>
-      <c r="E135" s="47" t="s">
+      <c r="D135" s="40"/>
+      <c r="E135" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="F135" s="47"/>
+      <c r="F135" s="54"/>
       <c r="G135" s="8">
         <v>2</v>
       </c>
@@ -11041,16 +11041,16 @@
       </c>
     </row>
     <row r="136" spans="1:32" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A136" s="42"/>
-      <c r="B136" s="42"/>
-      <c r="C136" s="46" t="s">
+      <c r="A136" s="45"/>
+      <c r="B136" s="45"/>
+      <c r="C136" s="40" t="s">
         <v>187</v>
       </c>
-      <c r="D136" s="46"/>
-      <c r="E136" s="47" t="s">
+      <c r="D136" s="40"/>
+      <c r="E136" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="F136" s="47"/>
+      <c r="F136" s="54"/>
       <c r="G136" s="8">
         <v>1</v>
       </c>
@@ -11107,16 +11107,16 @@
       </c>
     </row>
     <row r="137" spans="1:32" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A137" s="42"/>
-      <c r="B137" s="42"/>
-      <c r="C137" s="46" t="s">
+      <c r="A137" s="45"/>
+      <c r="B137" s="45"/>
+      <c r="C137" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="D137" s="46"/>
-      <c r="E137" s="47" t="s">
+      <c r="D137" s="40"/>
+      <c r="E137" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="F137" s="47"/>
+      <c r="F137" s="54"/>
       <c r="G137" s="8">
         <v>2</v>
       </c>
@@ -11173,16 +11173,16 @@
       </c>
     </row>
     <row r="138" spans="1:32" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A138" s="42"/>
-      <c r="B138" s="42"/>
-      <c r="C138" s="46" t="s">
+      <c r="A138" s="45"/>
+      <c r="B138" s="45"/>
+      <c r="C138" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="D138" s="46"/>
-      <c r="E138" s="47" t="s">
+      <c r="D138" s="40"/>
+      <c r="E138" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="F138" s="47"/>
+      <c r="F138" s="54"/>
       <c r="G138" s="8">
         <v>1</v>
       </c>
@@ -11239,16 +11239,16 @@
       </c>
     </row>
     <row r="139" spans="1:32" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A139" s="42"/>
-      <c r="B139" s="40"/>
-      <c r="C139" s="46" t="s">
+      <c r="A139" s="45"/>
+      <c r="B139" s="53"/>
+      <c r="C139" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="D139" s="46"/>
-      <c r="E139" s="47" t="s">
+      <c r="D139" s="40"/>
+      <c r="E139" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="F139" s="47"/>
+      <c r="F139" s="54"/>
       <c r="G139" s="8">
         <f t="shared" si="6"/>
         <v>2</v>
@@ -11306,18 +11306,18 @@
       </c>
     </row>
     <row r="140" spans="1:32" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A140" s="42"/>
-      <c r="B140" s="40" t="s">
+      <c r="A140" s="45"/>
+      <c r="B140" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="C140" s="41" t="s">
+      <c r="C140" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="D140" s="41"/>
-      <c r="E140" s="42" t="s">
+      <c r="D140" s="46"/>
+      <c r="E140" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="F140" s="42"/>
+      <c r="F140" s="45"/>
       <c r="G140" s="8">
         <f t="shared" si="6"/>
         <v>6</v>
@@ -11375,16 +11375,16 @@
       </c>
     </row>
     <row r="141" spans="1:32" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A141" s="42"/>
-      <c r="B141" s="40"/>
-      <c r="C141" s="41" t="s">
+      <c r="A141" s="45"/>
+      <c r="B141" s="53"/>
+      <c r="C141" s="46" t="s">
         <v>130</v>
       </c>
-      <c r="D141" s="41"/>
-      <c r="E141" s="42" t="s">
+      <c r="D141" s="46"/>
+      <c r="E141" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="F141" s="42"/>
+      <c r="F141" s="45"/>
       <c r="G141" s="8">
         <f t="shared" si="6"/>
         <v>6</v>
@@ -11442,21 +11442,21 @@
       </c>
     </row>
     <row r="142" spans="1:32" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A142" s="42"/>
-      <c r="B142" s="43" t="s">
+      <c r="A142" s="45"/>
+      <c r="B142" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="C142" s="43"/>
-      <c r="D142" s="43"/>
-      <c r="E142" s="43" t="s">
+      <c r="C142" s="55"/>
+      <c r="D142" s="55"/>
+      <c r="E142" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="F142" s="43"/>
-      <c r="G142" s="44">
+      <c r="F142" s="55"/>
+      <c r="G142" s="56">
         <f>SUM(G16:G141)</f>
         <v>310.5</v>
       </c>
-      <c r="H142" s="45"/>
+      <c r="H142" s="57"/>
       <c r="I142" s="8">
         <f t="shared" ref="I142:X142" si="7">SUM(I16:I141)</f>
         <v>286.5</v>
@@ -11523,19 +11523,19 @@
       </c>
     </row>
     <row r="143" spans="1:32" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A143" s="42"/>
-      <c r="B143" s="42"/>
-      <c r="C143" s="43"/>
-      <c r="D143" s="43"/>
-      <c r="E143" s="43" t="s">
+      <c r="A143" s="45"/>
+      <c r="B143" s="45"/>
+      <c r="C143" s="55"/>
+      <c r="D143" s="55"/>
+      <c r="E143" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="F143" s="43"/>
-      <c r="G143" s="44">
+      <c r="F143" s="55"/>
+      <c r="G143" s="56">
         <f>SUM(H16:H141)</f>
         <v>298.5</v>
       </c>
-      <c r="H143" s="45"/>
+      <c r="H143" s="57"/>
       <c r="I143" s="36">
         <f t="shared" ref="I143:X143" si="8">SUMIFS(I$16:I$141,$H$16:$H$141,"&gt;0")</f>
         <v>286.5</v>
@@ -11637,6 +11637,251 @@
     </row>
   </sheetData>
   <mergeCells count="269">
+    <mergeCell ref="B142:D143"/>
+    <mergeCell ref="E142:F142"/>
+    <mergeCell ref="E143:F143"/>
+    <mergeCell ref="G142:H142"/>
+    <mergeCell ref="G143:H143"/>
+    <mergeCell ref="E132:F132"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="E133:F133"/>
+    <mergeCell ref="C134:D134"/>
+    <mergeCell ref="E134:F134"/>
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="E139:F139"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="C140:D140"/>
+    <mergeCell ref="E140:F140"/>
+    <mergeCell ref="C141:D141"/>
+    <mergeCell ref="E141:F141"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="E136:F136"/>
+    <mergeCell ref="E137:F137"/>
+    <mergeCell ref="E138:F138"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="B124:B139"/>
+    <mergeCell ref="C124:D124"/>
+    <mergeCell ref="E124:F124"/>
+    <mergeCell ref="C125:D125"/>
+    <mergeCell ref="E125:F125"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="E126:F126"/>
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="E127:F127"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="E128:F128"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="E129:F129"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="E130:F130"/>
+    <mergeCell ref="C131:D131"/>
+    <mergeCell ref="E131:F131"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="B108:B123"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="E109:F109"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="E110:F110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="E111:F111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="E112:F112"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="E113:F113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="E114:F114"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="E115:F115"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="E116:F116"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="E117:F117"/>
+    <mergeCell ref="C118:D118"/>
+    <mergeCell ref="E118:F118"/>
+    <mergeCell ref="C123:D123"/>
+    <mergeCell ref="B92:B107"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="E94:F94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="E95:F95"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="E96:F96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="E97:F97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="E98:F98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="E99:F99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="E100:F100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="E101:F101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="B56:B91"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="B39:B55"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:A143"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B19:B38"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="E81:F81"/>
+    <mergeCell ref="E82:F82"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="E85:F85"/>
+    <mergeCell ref="E86:F86"/>
+    <mergeCell ref="E88:F88"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="E84:F84"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="E87:F87"/>
     <mergeCell ref="C137:D137"/>
     <mergeCell ref="C138:D138"/>
     <mergeCell ref="C90:D90"/>
@@ -11661,251 +11906,6 @@
     <mergeCell ref="E91:F91"/>
     <mergeCell ref="E107:F107"/>
     <mergeCell ref="E123:F123"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="E80:F80"/>
-    <mergeCell ref="E81:F81"/>
-    <mergeCell ref="E82:F82"/>
-    <mergeCell ref="E83:F83"/>
-    <mergeCell ref="E85:F85"/>
-    <mergeCell ref="E86:F86"/>
-    <mergeCell ref="E88:F88"/>
-    <mergeCell ref="E89:F89"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="E84:F84"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:A143"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B19:B38"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="B39:B55"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="B56:B91"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="E101:F101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="E103:F103"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="E79:F79"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="E116:F116"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="E117:F117"/>
-    <mergeCell ref="C118:D118"/>
-    <mergeCell ref="E118:F118"/>
-    <mergeCell ref="C123:D123"/>
-    <mergeCell ref="B92:B107"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="E92:F92"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="E94:F94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="E95:F95"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="E96:F96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="E97:F97"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="E98:F98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="E99:F99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="E100:F100"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="E129:F129"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="E130:F130"/>
-    <mergeCell ref="C131:D131"/>
-    <mergeCell ref="E131:F131"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="B108:B123"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="E108:F108"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="E109:F109"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="E110:F110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="E111:F111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="E112:F112"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="E113:F113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="E114:F114"/>
-    <mergeCell ref="C115:D115"/>
-    <mergeCell ref="E115:F115"/>
-    <mergeCell ref="C124:D124"/>
-    <mergeCell ref="E124:F124"/>
-    <mergeCell ref="C125:D125"/>
-    <mergeCell ref="E125:F125"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="E126:F126"/>
-    <mergeCell ref="C127:D127"/>
-    <mergeCell ref="E127:F127"/>
-    <mergeCell ref="C128:D128"/>
-    <mergeCell ref="E128:F128"/>
-    <mergeCell ref="B142:D143"/>
-    <mergeCell ref="E142:F142"/>
-    <mergeCell ref="E143:F143"/>
-    <mergeCell ref="G142:H142"/>
-    <mergeCell ref="G143:H143"/>
-    <mergeCell ref="E132:F132"/>
-    <mergeCell ref="C133:D133"/>
-    <mergeCell ref="E133:F133"/>
-    <mergeCell ref="C134:D134"/>
-    <mergeCell ref="E134:F134"/>
-    <mergeCell ref="C139:D139"/>
-    <mergeCell ref="E139:F139"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="C140:D140"/>
-    <mergeCell ref="E140:F140"/>
-    <mergeCell ref="C141:D141"/>
-    <mergeCell ref="E141:F141"/>
-    <mergeCell ref="E135:F135"/>
-    <mergeCell ref="E136:F136"/>
-    <mergeCell ref="E137:F137"/>
-    <mergeCell ref="E138:F138"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="C136:D136"/>
-    <mergeCell ref="B124:B139"/>
   </mergeCells>
   <pageMargins left="1.1811023622047243" right="0.59055118110236215" top="0.78740157480314954" bottom="0.78740157480314954" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -12118,12 +12118,12 @@
     </row>
     <row r="6" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="51" t="s">
         <v>133</v>
       </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
@@ -12414,10 +12414,10 @@
     </row>
     <row r="13" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
-      <c r="B13" s="54" t="s">
+      <c r="B13" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="54"/>
+      <c r="C13" s="51"/>
       <c r="D13" s="19">
         <f>SUM(D8:D12)</f>
         <v>217</v>
@@ -12491,14 +12491,14 @@
       <c r="B15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="55" t="s">
+      <c r="C15" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55" t="s">
+      <c r="D15" s="52"/>
+      <c r="E15" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="55"/>
+      <c r="F15" s="52"/>
       <c r="G15" s="1" t="s">
         <v>14</v>
       </c>
@@ -12575,18 +12575,18 @@
       </c>
     </row>
     <row r="16" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="42" t="s">
+      <c r="A16" s="45" t="s">
         <v>132</v>
       </c>
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="42" t="s">
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="42"/>
+      <c r="F16" s="45"/>
       <c r="G16" s="8">
         <v>5</v>
       </c>
@@ -12646,16 +12646,16 @@
       </c>
     </row>
     <row r="17" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="42"/>
-      <c r="B17" s="41" t="s">
+      <c r="A17" s="45"/>
+      <c r="B17" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="42" t="s">
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="42"/>
+      <c r="F17" s="45"/>
       <c r="G17" s="8">
         <v>5</v>
       </c>
@@ -12715,16 +12715,16 @@
       </c>
     </row>
     <row r="18" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="42"/>
-      <c r="B18" s="41" t="s">
+      <c r="A18" s="45"/>
+      <c r="B18" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="42" t="s">
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="42"/>
+      <c r="F18" s="45"/>
       <c r="G18" s="8">
         <v>2</v>
       </c>
@@ -12784,18 +12784,18 @@
       </c>
     </row>
     <row r="19" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="42"/>
-      <c r="B19" s="40" t="s">
+      <c r="A19" s="45"/>
+      <c r="B19" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="41" t="s">
+      <c r="C19" s="46" t="s">
         <v>135</v>
       </c>
-      <c r="D19" s="41"/>
-      <c r="E19" s="42" t="s">
+      <c r="D19" s="46"/>
+      <c r="E19" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="F19" s="42"/>
+      <c r="F19" s="45"/>
       <c r="G19" s="8">
         <v>6</v>
       </c>
@@ -12855,12 +12855,12 @@
       </c>
     </row>
     <row r="20" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="42"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="53"/>
+      <c r="A20" s="45"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="48"/>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
@@ -12886,16 +12886,16 @@
       </c>
     </row>
     <row r="21" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="42"/>
-      <c r="B21" s="42"/>
-      <c r="C21" s="41" t="s">
+      <c r="A21" s="45"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="46" t="s">
         <v>136</v>
       </c>
-      <c r="D21" s="41"/>
-      <c r="E21" s="42" t="s">
+      <c r="D21" s="46"/>
+      <c r="E21" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="F21" s="42"/>
+      <c r="F21" s="45"/>
       <c r="G21" s="8">
         <v>6</v>
       </c>
@@ -12955,12 +12955,12 @@
       </c>
     </row>
     <row r="22" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="42"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="52"/>
-      <c r="F22" s="53"/>
+      <c r="A22" s="45"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="48"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
@@ -12986,16 +12986,16 @@
       </c>
     </row>
     <row r="23" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="42"/>
-      <c r="B23" s="42"/>
-      <c r="C23" s="41" t="s">
+      <c r="A23" s="45"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="46" t="s">
         <v>137</v>
       </c>
-      <c r="D23" s="41"/>
-      <c r="E23" s="42" t="s">
+      <c r="D23" s="46"/>
+      <c r="E23" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="F23" s="42"/>
+      <c r="F23" s="45"/>
       <c r="G23" s="8">
         <v>6</v>
       </c>
@@ -13055,12 +13055,12 @@
       </c>
     </row>
     <row r="24" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="42"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="53"/>
+      <c r="A24" s="45"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="48"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
@@ -13086,16 +13086,16 @@
       </c>
     </row>
     <row r="25" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="42"/>
-      <c r="B25" s="42"/>
-      <c r="C25" s="41" t="s">
+      <c r="A25" s="45"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="46" t="s">
         <v>138</v>
       </c>
-      <c r="D25" s="41"/>
-      <c r="E25" s="42" t="s">
+      <c r="D25" s="46"/>
+      <c r="E25" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="F25" s="42"/>
+      <c r="F25" s="45"/>
       <c r="G25" s="8">
         <v>6</v>
       </c>
@@ -13155,12 +13155,12 @@
       </c>
     </row>
     <row r="26" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="42"/>
-      <c r="B26" s="42"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="52"/>
-      <c r="F26" s="53"/>
+      <c r="A26" s="45"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="48"/>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
@@ -13186,16 +13186,16 @@
       </c>
     </row>
     <row r="27" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="42"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="41" t="s">
+      <c r="A27" s="45"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="46" t="s">
         <v>139</v>
       </c>
-      <c r="D27" s="41"/>
-      <c r="E27" s="42" t="s">
+      <c r="D27" s="46"/>
+      <c r="E27" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F27" s="42"/>
+      <c r="F27" s="45"/>
       <c r="G27" s="8">
         <f t="shared" ref="G27:G54" si="1">H27</f>
         <v>2</v>
@@ -13256,16 +13256,16 @@
       </c>
     </row>
     <row r="28" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="42"/>
-      <c r="B28" s="42"/>
-      <c r="C28" s="41" t="s">
+      <c r="A28" s="45"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="46" t="s">
         <v>140</v>
       </c>
-      <c r="D28" s="41"/>
-      <c r="E28" s="42" t="s">
+      <c r="D28" s="46"/>
+      <c r="E28" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F28" s="42"/>
+      <c r="F28" s="45"/>
       <c r="G28" s="8">
         <f>H28</f>
         <v>2</v>
@@ -13326,16 +13326,16 @@
       </c>
     </row>
     <row r="29" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="42"/>
-      <c r="B29" s="40"/>
-      <c r="C29" s="41" t="s">
+      <c r="A29" s="45"/>
+      <c r="B29" s="53"/>
+      <c r="C29" s="46" t="s">
         <v>141</v>
       </c>
-      <c r="D29" s="41"/>
-      <c r="E29" s="42" t="s">
+      <c r="D29" s="46"/>
+      <c r="E29" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F29" s="42"/>
+      <c r="F29" s="45"/>
       <c r="G29" s="8">
         <v>2</v>
       </c>
@@ -13395,18 +13395,18 @@
       </c>
     </row>
     <row r="30" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="42"/>
-      <c r="B30" s="40" t="s">
+      <c r="A30" s="45"/>
+      <c r="B30" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="C30" s="48" t="s">
+      <c r="C30" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="D30" s="49"/>
-      <c r="E30" s="50" t="s">
+      <c r="D30" s="44"/>
+      <c r="E30" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="51"/>
+      <c r="F30" s="42"/>
       <c r="G30" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
@@ -13467,16 +13467,16 @@
       </c>
     </row>
     <row r="31" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="42"/>
-      <c r="B31" s="42"/>
-      <c r="C31" s="48" t="s">
+      <c r="A31" s="45"/>
+      <c r="B31" s="45"/>
+      <c r="C31" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="D31" s="49"/>
-      <c r="E31" s="50" t="s">
+      <c r="D31" s="44"/>
+      <c r="E31" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F31" s="51"/>
+      <c r="F31" s="42"/>
       <c r="G31" s="8">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -13537,16 +13537,16 @@
       </c>
     </row>
     <row r="32" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="42"/>
-      <c r="B32" s="42"/>
-      <c r="C32" s="48" t="s">
+      <c r="A32" s="45"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="43" t="s">
         <v>190</v>
       </c>
-      <c r="D32" s="49"/>
-      <c r="E32" s="50" t="s">
+      <c r="D32" s="44"/>
+      <c r="E32" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F32" s="51"/>
+      <c r="F32" s="42"/>
       <c r="G32" s="8">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -13607,16 +13607,16 @@
       </c>
     </row>
     <row r="33" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="42"/>
-      <c r="B33" s="42"/>
-      <c r="C33" s="48" t="s">
+      <c r="A33" s="45"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="43" t="s">
         <v>191</v>
       </c>
-      <c r="D33" s="49"/>
-      <c r="E33" s="50" t="s">
+      <c r="D33" s="44"/>
+      <c r="E33" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F33" s="51"/>
+      <c r="F33" s="42"/>
       <c r="G33" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
@@ -13677,16 +13677,16 @@
       </c>
     </row>
     <row r="34" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="42"/>
-      <c r="B34" s="42"/>
-      <c r="C34" s="48" t="s">
+      <c r="A34" s="45"/>
+      <c r="B34" s="45"/>
+      <c r="C34" s="43" t="s">
         <v>192</v>
       </c>
-      <c r="D34" s="49"/>
-      <c r="E34" s="50" t="s">
+      <c r="D34" s="44"/>
+      <c r="E34" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F34" s="51"/>
+      <c r="F34" s="42"/>
       <c r="G34" s="8">
         <f t="shared" si="1"/>
         <v>3</v>
@@ -13747,16 +13747,16 @@
       </c>
     </row>
     <row r="35" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="42"/>
-      <c r="B35" s="42"/>
-      <c r="C35" s="48" t="s">
+      <c r="A35" s="45"/>
+      <c r="B35" s="45"/>
+      <c r="C35" s="43" t="s">
         <v>193</v>
       </c>
-      <c r="D35" s="49"/>
-      <c r="E35" s="50" t="s">
+      <c r="D35" s="44"/>
+      <c r="E35" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="F35" s="51"/>
+      <c r="F35" s="42"/>
       <c r="G35" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
@@ -13817,16 +13817,16 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="42"/>
-      <c r="B36" s="42"/>
-      <c r="C36" s="48" t="s">
+      <c r="A36" s="45"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="D36" s="49"/>
-      <c r="E36" s="50" t="s">
+      <c r="D36" s="44"/>
+      <c r="E36" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F36" s="51"/>
+      <c r="F36" s="42"/>
       <c r="G36" s="8">
         <v>3</v>
       </c>
@@ -13886,16 +13886,16 @@
       </c>
     </row>
     <row r="37" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="42"/>
-      <c r="B37" s="42"/>
-      <c r="C37" s="48" t="s">
+      <c r="A37" s="45"/>
+      <c r="B37" s="45"/>
+      <c r="C37" s="43" t="s">
         <v>194</v>
       </c>
-      <c r="D37" s="49"/>
-      <c r="E37" s="50" t="s">
+      <c r="D37" s="44"/>
+      <c r="E37" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F37" s="51"/>
+      <c r="F37" s="42"/>
       <c r="G37" s="8">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -13956,16 +13956,16 @@
       </c>
     </row>
     <row r="38" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="42"/>
-      <c r="B38" s="40"/>
-      <c r="C38" s="41" t="s">
+      <c r="A38" s="45"/>
+      <c r="B38" s="53"/>
+      <c r="C38" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="D38" s="41"/>
-      <c r="E38" s="42" t="s">
+      <c r="D38" s="46"/>
+      <c r="E38" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F38" s="42"/>
+      <c r="F38" s="45"/>
       <c r="G38" s="8">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -14026,18 +14026,18 @@
       </c>
     </row>
     <row r="39" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="42"/>
-      <c r="B39" s="40" t="s">
+      <c r="A39" s="45"/>
+      <c r="B39" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="C39" s="48" t="s">
+      <c r="C39" s="43" t="s">
         <v>145</v>
       </c>
-      <c r="D39" s="49"/>
-      <c r="E39" s="47" t="s">
+      <c r="D39" s="44"/>
+      <c r="E39" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="F39" s="47"/>
+      <c r="F39" s="54"/>
       <c r="G39" s="8">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -14098,16 +14098,16 @@
       </c>
     </row>
     <row r="40" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="42"/>
-      <c r="B40" s="42"/>
-      <c r="C40" s="48" t="s">
+      <c r="A40" s="45"/>
+      <c r="B40" s="45"/>
+      <c r="C40" s="43" t="s">
         <v>146</v>
       </c>
-      <c r="D40" s="49"/>
-      <c r="E40" s="47" t="s">
+      <c r="D40" s="44"/>
+      <c r="E40" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="F40" s="47"/>
+      <c r="F40" s="54"/>
       <c r="G40" s="8">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -14168,16 +14168,16 @@
       </c>
     </row>
     <row r="41" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="42"/>
-      <c r="B41" s="42"/>
-      <c r="C41" s="48" t="s">
+      <c r="A41" s="45"/>
+      <c r="B41" s="45"/>
+      <c r="C41" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="D41" s="49"/>
-      <c r="E41" s="47" t="s">
+      <c r="D41" s="44"/>
+      <c r="E41" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="F41" s="47"/>
+      <c r="F41" s="54"/>
       <c r="G41" s="8">
         <v>4</v>
       </c>
@@ -14237,16 +14237,16 @@
       </c>
     </row>
     <row r="42" spans="1:25" s="37" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="42"/>
-      <c r="B42" s="42"/>
-      <c r="C42" s="48" t="s">
+      <c r="A42" s="45"/>
+      <c r="B42" s="45"/>
+      <c r="C42" s="43" t="s">
         <v>196</v>
       </c>
-      <c r="D42" s="49"/>
-      <c r="E42" s="47" t="s">
+      <c r="D42" s="44"/>
+      <c r="E42" s="54" t="s">
         <v>147</v>
       </c>
-      <c r="F42" s="47"/>
+      <c r="F42" s="54"/>
       <c r="G42" s="38">
         <v>10</v>
       </c>
@@ -14306,16 +14306,16 @@
       </c>
     </row>
     <row r="43" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="42"/>
-      <c r="B43" s="42"/>
-      <c r="C43" s="48" t="s">
+      <c r="A43" s="45"/>
+      <c r="B43" s="45"/>
+      <c r="C43" s="43" t="s">
         <v>197</v>
       </c>
-      <c r="D43" s="49"/>
-      <c r="E43" s="47" t="s">
+      <c r="D43" s="44"/>
+      <c r="E43" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="F43" s="47"/>
+      <c r="F43" s="54"/>
       <c r="G43" s="8">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -14376,16 +14376,16 @@
       </c>
     </row>
     <row r="44" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="42"/>
-      <c r="B44" s="42"/>
-      <c r="C44" s="48" t="s">
+      <c r="A44" s="45"/>
+      <c r="B44" s="45"/>
+      <c r="C44" s="43" t="s">
         <v>198</v>
       </c>
-      <c r="D44" s="49"/>
-      <c r="E44" s="47" t="s">
+      <c r="D44" s="44"/>
+      <c r="E44" s="54" t="s">
         <v>147</v>
       </c>
-      <c r="F44" s="47"/>
+      <c r="F44" s="54"/>
       <c r="G44" s="8">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -14446,16 +14446,16 @@
       </c>
     </row>
     <row r="45" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="42"/>
-      <c r="B45" s="42"/>
-      <c r="C45" s="48" t="s">
+      <c r="A45" s="45"/>
+      <c r="B45" s="45"/>
+      <c r="C45" s="43" t="s">
         <v>199</v>
       </c>
-      <c r="D45" s="49"/>
-      <c r="E45" s="47" t="s">
+      <c r="D45" s="44"/>
+      <c r="E45" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="F45" s="47"/>
+      <c r="F45" s="54"/>
       <c r="G45" s="8">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -14516,16 +14516,16 @@
       </c>
     </row>
     <row r="46" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="42"/>
-      <c r="B46" s="42"/>
-      <c r="C46" s="48" t="s">
+      <c r="A46" s="45"/>
+      <c r="B46" s="45"/>
+      <c r="C46" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="D46" s="49"/>
-      <c r="E46" s="47" t="s">
+      <c r="D46" s="44"/>
+      <c r="E46" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="F46" s="47"/>
+      <c r="F46" s="54"/>
       <c r="G46" s="8">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -14586,16 +14586,16 @@
       </c>
     </row>
     <row r="47" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="42"/>
-      <c r="B47" s="42"/>
-      <c r="C47" s="48" t="s">
+      <c r="A47" s="45"/>
+      <c r="B47" s="45"/>
+      <c r="C47" s="43" t="s">
         <v>201</v>
       </c>
-      <c r="D47" s="49"/>
-      <c r="E47" s="47" t="s">
+      <c r="D47" s="44"/>
+      <c r="E47" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="F47" s="47"/>
+      <c r="F47" s="54"/>
       <c r="G47" s="8">
         <f t="shared" si="1"/>
         <v>3</v>
@@ -14656,16 +14656,16 @@
       </c>
     </row>
     <row r="48" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="42"/>
-      <c r="B48" s="42"/>
-      <c r="C48" s="48" t="s">
+      <c r="A48" s="45"/>
+      <c r="B48" s="45"/>
+      <c r="C48" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="D48" s="49"/>
-      <c r="E48" s="47" t="s">
+      <c r="D48" s="44"/>
+      <c r="E48" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="F48" s="47"/>
+      <c r="F48" s="54"/>
       <c r="G48" s="8">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -14726,16 +14726,16 @@
       </c>
     </row>
     <row r="49" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="42"/>
-      <c r="B49" s="42"/>
-      <c r="C49" s="48" t="s">
+      <c r="A49" s="45"/>
+      <c r="B49" s="45"/>
+      <c r="C49" s="43" t="s">
         <v>203</v>
       </c>
-      <c r="D49" s="49"/>
-      <c r="E49" s="47" t="s">
+      <c r="D49" s="44"/>
+      <c r="E49" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="F49" s="47"/>
+      <c r="F49" s="54"/>
       <c r="G49" s="8">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -14796,16 +14796,16 @@
       </c>
     </row>
     <row r="50" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="42"/>
-      <c r="B50" s="42"/>
-      <c r="C50" s="48" t="s">
+      <c r="A50" s="45"/>
+      <c r="B50" s="45"/>
+      <c r="C50" s="43" t="s">
         <v>204</v>
       </c>
-      <c r="D50" s="49"/>
-      <c r="E50" s="47" t="s">
+      <c r="D50" s="44"/>
+      <c r="E50" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="F50" s="47"/>
+      <c r="F50" s="54"/>
       <c r="G50" s="8">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -14866,16 +14866,16 @@
       </c>
     </row>
     <row r="51" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="42"/>
-      <c r="B51" s="42"/>
-      <c r="C51" s="48" t="s">
+      <c r="A51" s="45"/>
+      <c r="B51" s="45"/>
+      <c r="C51" s="43" t="s">
         <v>148</v>
       </c>
-      <c r="D51" s="49"/>
-      <c r="E51" s="47" t="s">
+      <c r="D51" s="44"/>
+      <c r="E51" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="F51" s="47"/>
+      <c r="F51" s="54"/>
       <c r="G51" s="8">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -14936,16 +14936,16 @@
       </c>
     </row>
     <row r="52" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="42"/>
-      <c r="B52" s="42"/>
-      <c r="C52" s="48" t="s">
+      <c r="A52" s="45"/>
+      <c r="B52" s="45"/>
+      <c r="C52" s="43" t="s">
         <v>149</v>
       </c>
-      <c r="D52" s="49"/>
-      <c r="E52" s="47" t="s">
+      <c r="D52" s="44"/>
+      <c r="E52" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="F52" s="47"/>
+      <c r="F52" s="54"/>
       <c r="G52" s="8">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -15006,16 +15006,16 @@
       </c>
     </row>
     <row r="53" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="42"/>
-      <c r="B53" s="42"/>
-      <c r="C53" s="48" t="s">
+      <c r="A53" s="45"/>
+      <c r="B53" s="45"/>
+      <c r="C53" s="43" t="s">
         <v>205</v>
       </c>
-      <c r="D53" s="49"/>
-      <c r="E53" s="47" t="s">
+      <c r="D53" s="44"/>
+      <c r="E53" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="F53" s="47"/>
+      <c r="F53" s="54"/>
       <c r="G53" s="8">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -15076,16 +15076,16 @@
       </c>
     </row>
     <row r="54" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="42"/>
-      <c r="B54" s="42"/>
-      <c r="C54" s="48" t="s">
+      <c r="A54" s="45"/>
+      <c r="B54" s="45"/>
+      <c r="C54" s="43" t="s">
         <v>206</v>
       </c>
-      <c r="D54" s="49"/>
-      <c r="E54" s="47" t="s">
+      <c r="D54" s="44"/>
+      <c r="E54" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="F54" s="47"/>
+      <c r="F54" s="54"/>
       <c r="G54" s="8">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -15146,16 +15146,16 @@
       </c>
     </row>
     <row r="55" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="42"/>
-      <c r="B55" s="40"/>
-      <c r="C55" s="41" t="s">
+      <c r="A55" s="45"/>
+      <c r="B55" s="53"/>
+      <c r="C55" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="D55" s="41"/>
-      <c r="E55" s="42" t="s">
+      <c r="D55" s="46"/>
+      <c r="E55" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F55" s="42"/>
+      <c r="F55" s="45"/>
       <c r="G55" s="8">
         <f t="shared" ref="G55:G81" si="2">H55</f>
         <v>10</v>
@@ -15216,18 +15216,18 @@
       </c>
     </row>
     <row r="56" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="42"/>
-      <c r="B56" s="40" t="s">
+      <c r="A56" s="45"/>
+      <c r="B56" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="C56" s="48" t="s">
+      <c r="C56" s="43" t="s">
         <v>150</v>
       </c>
-      <c r="D56" s="49"/>
-      <c r="E56" s="50" t="s">
+      <c r="D56" s="44"/>
+      <c r="E56" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F56" s="51"/>
+      <c r="F56" s="42"/>
       <c r="G56" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
@@ -15288,16 +15288,16 @@
       </c>
     </row>
     <row r="57" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="42"/>
-      <c r="B57" s="42"/>
-      <c r="C57" s="48" t="s">
+      <c r="A57" s="45"/>
+      <c r="B57" s="45"/>
+      <c r="C57" s="43" t="s">
         <v>207</v>
       </c>
-      <c r="D57" s="49"/>
-      <c r="E57" s="50" t="s">
+      <c r="D57" s="44"/>
+      <c r="E57" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F57" s="51"/>
+      <c r="F57" s="42"/>
       <c r="G57" s="8">
         <f t="shared" si="2"/>
         <v>3</v>
@@ -15358,16 +15358,16 @@
       </c>
     </row>
     <row r="58" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="42"/>
-      <c r="B58" s="42"/>
-      <c r="C58" s="48" t="s">
+      <c r="A58" s="45"/>
+      <c r="B58" s="45"/>
+      <c r="C58" s="43" t="s">
         <v>208</v>
       </c>
-      <c r="D58" s="49"/>
-      <c r="E58" s="50" t="s">
+      <c r="D58" s="44"/>
+      <c r="E58" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F58" s="51"/>
+      <c r="F58" s="42"/>
       <c r="G58" s="8">
         <f t="shared" si="2"/>
         <v>3</v>
@@ -15428,16 +15428,16 @@
       </c>
     </row>
     <row r="59" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="42"/>
-      <c r="B59" s="42"/>
-      <c r="C59" s="48" t="s">
+      <c r="A59" s="45"/>
+      <c r="B59" s="45"/>
+      <c r="C59" s="43" t="s">
         <v>209</v>
       </c>
-      <c r="D59" s="49"/>
-      <c r="E59" s="50" t="s">
+      <c r="D59" s="44"/>
+      <c r="E59" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F59" s="51"/>
+      <c r="F59" s="42"/>
       <c r="G59" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
@@ -15498,16 +15498,16 @@
       </c>
     </row>
     <row r="60" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="42"/>
-      <c r="B60" s="42"/>
-      <c r="C60" s="48" t="s">
+      <c r="A60" s="45"/>
+      <c r="B60" s="45"/>
+      <c r="C60" s="43" t="s">
         <v>210</v>
       </c>
-      <c r="D60" s="49"/>
-      <c r="E60" s="50" t="s">
+      <c r="D60" s="44"/>
+      <c r="E60" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F60" s="51"/>
+      <c r="F60" s="42"/>
       <c r="G60" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
@@ -15568,16 +15568,16 @@
       </c>
     </row>
     <row r="61" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="42"/>
-      <c r="B61" s="42"/>
-      <c r="C61" s="48" t="s">
+      <c r="A61" s="45"/>
+      <c r="B61" s="45"/>
+      <c r="C61" s="43" t="s">
         <v>211</v>
       </c>
-      <c r="D61" s="49"/>
-      <c r="E61" s="50" t="s">
+      <c r="D61" s="44"/>
+      <c r="E61" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="F61" s="51"/>
+      <c r="F61" s="42"/>
       <c r="G61" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
@@ -15638,16 +15638,16 @@
       </c>
     </row>
     <row r="62" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="42"/>
-      <c r="B62" s="42"/>
-      <c r="C62" s="48" t="s">
+      <c r="A62" s="45"/>
+      <c r="B62" s="45"/>
+      <c r="C62" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="D62" s="49"/>
-      <c r="E62" s="50" t="s">
+      <c r="D62" s="44"/>
+      <c r="E62" s="41" t="s">
         <v>152</v>
       </c>
-      <c r="F62" s="51"/>
+      <c r="F62" s="42"/>
       <c r="G62" s="8">
         <v>2</v>
       </c>
@@ -15707,16 +15707,16 @@
       </c>
     </row>
     <row r="63" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="42"/>
-      <c r="B63" s="40"/>
-      <c r="C63" s="48" t="s">
+      <c r="A63" s="45"/>
+      <c r="B63" s="53"/>
+      <c r="C63" s="43" t="s">
         <v>212</v>
       </c>
-      <c r="D63" s="49"/>
-      <c r="E63" s="50" t="s">
+      <c r="D63" s="44"/>
+      <c r="E63" s="41" t="s">
         <v>152</v>
       </c>
-      <c r="F63" s="51"/>
+      <c r="F63" s="42"/>
       <c r="G63" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
@@ -15777,18 +15777,18 @@
       </c>
     </row>
     <row r="64" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="42"/>
-      <c r="B64" s="40" t="s">
+      <c r="A64" s="45"/>
+      <c r="B64" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="C64" s="48" t="s">
+      <c r="C64" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="D64" s="49"/>
-      <c r="E64" s="42" t="s">
+      <c r="D64" s="44"/>
+      <c r="E64" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F64" s="42"/>
+      <c r="F64" s="45"/>
       <c r="G64" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
@@ -15849,16 +15849,16 @@
       </c>
     </row>
     <row r="65" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="42"/>
-      <c r="B65" s="42"/>
-      <c r="C65" s="48" t="s">
+      <c r="A65" s="45"/>
+      <c r="B65" s="45"/>
+      <c r="C65" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="D65" s="49"/>
-      <c r="E65" s="42" t="s">
+      <c r="D65" s="44"/>
+      <c r="E65" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F65" s="42"/>
+      <c r="F65" s="45"/>
       <c r="G65" s="8">
         <f t="shared" si="2"/>
         <v>3</v>
@@ -15919,16 +15919,16 @@
       </c>
     </row>
     <row r="66" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="42"/>
-      <c r="B66" s="42"/>
-      <c r="C66" s="48" t="s">
+      <c r="A66" s="45"/>
+      <c r="B66" s="45"/>
+      <c r="C66" s="43" t="s">
         <v>213</v>
       </c>
-      <c r="D66" s="49"/>
-      <c r="E66" s="42" t="s">
+      <c r="D66" s="44"/>
+      <c r="E66" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F66" s="42"/>
+      <c r="F66" s="45"/>
       <c r="G66" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -15989,16 +15989,16 @@
       </c>
     </row>
     <row r="67" spans="1:25" s="37" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="42"/>
-      <c r="B67" s="42"/>
-      <c r="C67" s="48" t="s">
+      <c r="A67" s="45"/>
+      <c r="B67" s="45"/>
+      <c r="C67" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="D67" s="49"/>
-      <c r="E67" s="42" t="s">
+      <c r="D67" s="44"/>
+      <c r="E67" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F67" s="42"/>
+      <c r="F67" s="45"/>
       <c r="G67" s="38">
         <v>2</v>
       </c>
@@ -16058,16 +16058,16 @@
       </c>
     </row>
     <row r="68" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="42"/>
-      <c r="B68" s="42"/>
-      <c r="C68" s="48" t="s">
+      <c r="A68" s="45"/>
+      <c r="B68" s="45"/>
+      <c r="C68" s="43" t="s">
         <v>214</v>
       </c>
-      <c r="D68" s="49"/>
-      <c r="E68" s="42" t="s">
+      <c r="D68" s="44"/>
+      <c r="E68" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F68" s="42"/>
+      <c r="F68" s="45"/>
       <c r="G68" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -16128,16 +16128,16 @@
       </c>
     </row>
     <row r="69" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="42"/>
-      <c r="B69" s="42"/>
-      <c r="C69" s="48" t="s">
+      <c r="A69" s="45"/>
+      <c r="B69" s="45"/>
+      <c r="C69" s="43" t="s">
         <v>215</v>
       </c>
-      <c r="D69" s="49"/>
-      <c r="E69" s="42" t="s">
+      <c r="D69" s="44"/>
+      <c r="E69" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F69" s="42"/>
+      <c r="F69" s="45"/>
       <c r="G69" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -16198,16 +16198,16 @@
       </c>
     </row>
     <row r="70" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="42"/>
-      <c r="B70" s="42"/>
-      <c r="C70" s="48" t="s">
+      <c r="A70" s="45"/>
+      <c r="B70" s="45"/>
+      <c r="C70" s="43" t="s">
         <v>154</v>
       </c>
-      <c r="D70" s="49"/>
-      <c r="E70" s="42" t="s">
+      <c r="D70" s="44"/>
+      <c r="E70" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F70" s="42"/>
+      <c r="F70" s="45"/>
       <c r="G70" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -16268,16 +16268,16 @@
       </c>
     </row>
     <row r="71" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="42"/>
-      <c r="B71" s="40"/>
-      <c r="C71" s="48" t="s">
+      <c r="A71" s="45"/>
+      <c r="B71" s="53"/>
+      <c r="C71" s="43" t="s">
         <v>216</v>
       </c>
-      <c r="D71" s="49"/>
-      <c r="E71" s="42" t="s">
+      <c r="D71" s="44"/>
+      <c r="E71" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F71" s="42"/>
+      <c r="F71" s="45"/>
       <c r="G71" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -16338,18 +16338,18 @@
       </c>
     </row>
     <row r="72" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="42"/>
-      <c r="B72" s="40" t="s">
+      <c r="A72" s="45"/>
+      <c r="B72" s="53" t="s">
         <v>115</v>
       </c>
-      <c r="C72" s="46" t="s">
+      <c r="C72" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="D72" s="46"/>
-      <c r="E72" s="47" t="s">
+      <c r="D72" s="40"/>
+      <c r="E72" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="F72" s="47"/>
+      <c r="F72" s="54"/>
       <c r="G72" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
@@ -16410,16 +16410,16 @@
       </c>
     </row>
     <row r="73" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="42"/>
-      <c r="B73" s="42"/>
-      <c r="C73" s="46" t="s">
+      <c r="A73" s="45"/>
+      <c r="B73" s="45"/>
+      <c r="C73" s="40" t="s">
         <v>219</v>
       </c>
-      <c r="D73" s="46"/>
-      <c r="E73" s="47" t="s">
+      <c r="D73" s="40"/>
+      <c r="E73" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="F73" s="47"/>
+      <c r="F73" s="54"/>
       <c r="G73" s="8">
         <f t="shared" si="2"/>
         <v>3</v>
@@ -16480,16 +16480,16 @@
       </c>
     </row>
     <row r="74" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="42"/>
-      <c r="B74" s="42"/>
-      <c r="C74" s="46" t="s">
+      <c r="A74" s="45"/>
+      <c r="B74" s="45"/>
+      <c r="C74" s="40" t="s">
         <v>220</v>
       </c>
-      <c r="D74" s="46"/>
-      <c r="E74" s="47" t="s">
+      <c r="D74" s="40"/>
+      <c r="E74" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="F74" s="47"/>
+      <c r="F74" s="54"/>
       <c r="G74" s="8">
         <f t="shared" si="2"/>
         <v>3</v>
@@ -16550,16 +16550,16 @@
       </c>
     </row>
     <row r="75" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="42"/>
-      <c r="B75" s="42"/>
-      <c r="C75" s="46" t="s">
+      <c r="A75" s="45"/>
+      <c r="B75" s="45"/>
+      <c r="C75" s="40" t="s">
         <v>221</v>
       </c>
-      <c r="D75" s="46"/>
-      <c r="E75" s="47" t="s">
+      <c r="D75" s="40"/>
+      <c r="E75" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="F75" s="47"/>
+      <c r="F75" s="54"/>
       <c r="G75" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
@@ -16620,16 +16620,16 @@
       </c>
     </row>
     <row r="76" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="42"/>
-      <c r="B76" s="42"/>
-      <c r="C76" s="46" t="s">
+      <c r="A76" s="45"/>
+      <c r="B76" s="45"/>
+      <c r="C76" s="40" t="s">
         <v>222</v>
       </c>
-      <c r="D76" s="46"/>
-      <c r="E76" s="47" t="s">
+      <c r="D76" s="40"/>
+      <c r="E76" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="F76" s="47"/>
+      <c r="F76" s="54"/>
       <c r="G76" s="8">
         <v>2</v>
       </c>
@@ -16689,16 +16689,16 @@
       </c>
     </row>
     <row r="77" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="42"/>
-      <c r="B77" s="42"/>
-      <c r="C77" s="46" t="s">
+      <c r="A77" s="45"/>
+      <c r="B77" s="45"/>
+      <c r="C77" s="40" t="s">
         <v>223</v>
       </c>
-      <c r="D77" s="46"/>
-      <c r="E77" s="47" t="s">
+      <c r="D77" s="40"/>
+      <c r="E77" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="F77" s="47"/>
+      <c r="F77" s="54"/>
       <c r="G77" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
@@ -16759,16 +16759,16 @@
       </c>
     </row>
     <row r="78" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="42"/>
-      <c r="B78" s="42"/>
-      <c r="C78" s="46" t="s">
+      <c r="A78" s="45"/>
+      <c r="B78" s="45"/>
+      <c r="C78" s="40" t="s">
         <v>156</v>
       </c>
-      <c r="D78" s="46"/>
-      <c r="E78" s="47" t="s">
+      <c r="D78" s="40"/>
+      <c r="E78" s="54" t="s">
         <v>152</v>
       </c>
-      <c r="F78" s="47"/>
+      <c r="F78" s="54"/>
       <c r="G78" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
@@ -16829,16 +16829,16 @@
       </c>
     </row>
     <row r="79" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="42"/>
-      <c r="B79" s="40"/>
-      <c r="C79" s="46" t="s">
+      <c r="A79" s="45"/>
+      <c r="B79" s="53"/>
+      <c r="C79" s="40" t="s">
         <v>224</v>
       </c>
-      <c r="D79" s="46"/>
-      <c r="E79" s="47" t="s">
+      <c r="D79" s="40"/>
+      <c r="E79" s="54" t="s">
         <v>152</v>
       </c>
-      <c r="F79" s="47"/>
+      <c r="F79" s="54"/>
       <c r="G79" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
@@ -16899,18 +16899,18 @@
       </c>
     </row>
     <row r="80" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="42"/>
-      <c r="B80" s="40" t="s">
+      <c r="A80" s="45"/>
+      <c r="B80" s="53" t="s">
         <v>157</v>
       </c>
-      <c r="C80" s="41" t="s">
+      <c r="C80" s="46" t="s">
         <v>158</v>
       </c>
-      <c r="D80" s="41"/>
-      <c r="E80" s="42" t="s">
+      <c r="D80" s="46"/>
+      <c r="E80" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="F80" s="42"/>
+      <c r="F80" s="45"/>
       <c r="G80" s="8">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -16971,16 +16971,16 @@
       </c>
     </row>
     <row r="81" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="42"/>
-      <c r="B81" s="40"/>
-      <c r="C81" s="41" t="s">
+      <c r="A81" s="45"/>
+      <c r="B81" s="53"/>
+      <c r="C81" s="46" t="s">
         <v>159</v>
       </c>
-      <c r="D81" s="41"/>
-      <c r="E81" s="42" t="s">
+      <c r="D81" s="46"/>
+      <c r="E81" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="F81" s="42"/>
+      <c r="F81" s="45"/>
       <c r="G81" s="8">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -17041,21 +17041,21 @@
       </c>
     </row>
     <row r="82" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="42"/>
-      <c r="B82" s="43" t="s">
+      <c r="A82" s="45"/>
+      <c r="B82" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="C82" s="43"/>
-      <c r="D82" s="43"/>
-      <c r="E82" s="43" t="s">
+      <c r="C82" s="55"/>
+      <c r="D82" s="55"/>
+      <c r="E82" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="F82" s="43"/>
-      <c r="G82" s="44">
+      <c r="F82" s="55"/>
+      <c r="G82" s="56">
         <f>SUM(G16:G81)</f>
         <v>217</v>
       </c>
-      <c r="H82" s="45"/>
+      <c r="H82" s="57"/>
       <c r="I82" s="8">
         <f t="shared" ref="I82:Y82" si="3">SUM(I16:I81)</f>
         <v>201</v>
@@ -17126,19 +17126,19 @@
       </c>
     </row>
     <row r="83" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="42"/>
-      <c r="B83" s="42"/>
-      <c r="C83" s="43"/>
-      <c r="D83" s="43"/>
-      <c r="E83" s="43" t="s">
+      <c r="A83" s="45"/>
+      <c r="B83" s="45"/>
+      <c r="C83" s="55"/>
+      <c r="D83" s="55"/>
+      <c r="E83" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="F83" s="43"/>
-      <c r="G83" s="44">
+      <c r="F83" s="55"/>
+      <c r="G83" s="56">
         <f>SUM(H16:H81)</f>
         <v>201</v>
       </c>
-      <c r="H83" s="45"/>
+      <c r="H83" s="57"/>
       <c r="I83" s="22">
         <f>SUMIFS(I$16:I$81,$H$16:$H$81,"&gt;0")</f>
         <v>201</v>
@@ -17242,6 +17242,131 @@
     </row>
   </sheetData>
   <mergeCells count="149">
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="E81:F81"/>
+    <mergeCell ref="B82:D83"/>
+    <mergeCell ref="E82:F82"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="G82:H82"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="B72:B79"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="B64:B71"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="B56:B63"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="B39:B55"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="B30:B38"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="A16:A83"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B19:B29"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
     <mergeCell ref="C62:D62"/>
     <mergeCell ref="E62:F62"/>
     <mergeCell ref="C67:D67"/>
@@ -17266,131 +17391,6 @@
     <mergeCell ref="C49:D49"/>
     <mergeCell ref="E49:F49"/>
     <mergeCell ref="C50:D50"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:A83"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B19:B29"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="B30:B38"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="B56:B63"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="B39:B55"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="B64:B71"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="B72:B79"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="E79:F79"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="E80:F80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="E81:F81"/>
-    <mergeCell ref="B82:D83"/>
-    <mergeCell ref="E82:F82"/>
-    <mergeCell ref="E83:F83"/>
-    <mergeCell ref="G82:H82"/>
-    <mergeCell ref="G83:H83"/>
   </mergeCells>
   <pageMargins left="1.1811023622047243" right="0.59055118110236215" top="0.78740157480314954" bottom="0.78740157480314954" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
